--- a/howell7x3.xlsx
+++ b/howell7x3.xlsx
@@ -506,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Jun 18, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Jul 29, 2026.</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 63</t>
+          <t>Name 64</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 14</t>
+          <t>Name 47</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 31</t>
+          <t>Name 83</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 46</t>
+          <t>Name 68</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -636,12 +636,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 20</t>
+          <t>Name 54</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 46</t>
+          <t>Name 89</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -659,12 +659,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name 39</t>
+          <t>Name 88</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name 15</t>
+          <t>Name 13</t>
         </is>
       </c>
       <c r="D13" s="4">
@@ -682,12 +682,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name 56</t>
+          <t>Name 51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Name 49</t>
+          <t>Name 71</t>
         </is>
       </c>
       <c r="D14" s="4">
@@ -705,12 +705,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name 46</t>
+          <t>Name 52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name 47</t>
+          <t>Name 39</t>
         </is>
       </c>
       <c r="D15" s="4">
@@ -728,12 +728,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name 83</t>
+          <t>Name 21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Name 32</t>
+          <t>Name 78</t>
         </is>
       </c>
       <c r="D16" s="4">
@@ -1076,47 +1076,47 @@
     </row>
     <row r="4">
       <c r="B4" s="10">
-        <f>'By Round'!A63</f>
+        <f>'By Round'!A48</f>
         <v/>
       </c>
       <c r="C4" s="10">
-        <f>'By Round'!B69</f>
+        <f>'By Round'!B54</f>
         <v/>
       </c>
       <c r="D4" s="10">
-        <f>'By Round'!C69</f>
+        <f>'By Round'!C54</f>
         <v/>
       </c>
       <c r="E4" s="10">
-        <f>'By Round'!D69</f>
+        <f>'By Round'!D54</f>
         <v/>
       </c>
       <c r="F4" s="10">
-        <f>IF(ISBLANK('By Round'!F69),"",'By Round'!F69)</f>
+        <f>IF(ISBLANK('By Round'!F54),"",'By Round'!F54)</f>
         <v/>
       </c>
       <c r="G4">
-        <f>IF(ISBLANK('By Round'!G69),"",'By Round'!G69)</f>
+        <f>IF(ISBLANK('By Round'!G54),"",'By Round'!G54)</f>
         <v/>
       </c>
       <c r="H4">
-        <f>IF(ISBLANK('By Round'!H69),"",'By Round'!H69)</f>
+        <f>IF(ISBLANK('By Round'!H54),"",'By Round'!H54)</f>
         <v/>
       </c>
       <c r="I4">
-        <f>IF(ISBLANK('By Round'!I69),"",'By Round'!I69)</f>
+        <f>IF(ISBLANK('By Round'!I54),"",'By Round'!I54)</f>
         <v/>
       </c>
       <c r="J4">
-        <f>IF(ISBLANK('By Round'!J69),"",'By Round'!J69)</f>
+        <f>IF(ISBLANK('By Round'!J54),"",'By Round'!J54)</f>
         <v/>
       </c>
       <c r="K4">
-        <f>IF(ISBLANK('By Round'!K69),"",'By Round'!K69)</f>
+        <f>IF(ISBLANK('By Round'!K54),"",'By Round'!K54)</f>
         <v/>
       </c>
       <c r="L4">
-        <f>IF(ISBLANK('By Round'!L69),"",'By Round'!L69)</f>
+        <f>IF(ISBLANK('By Round'!L54),"",'By Round'!L54)</f>
         <v/>
       </c>
       <c r="M4" s="11">
@@ -1202,47 +1202,47 @@
     </row>
     <row r="5">
       <c r="B5" s="10">
-        <f>'By Round'!A39</f>
+        <f>'By Round'!A30</f>
         <v/>
       </c>
       <c r="C5" s="10">
-        <f>'By Round'!B48</f>
+        <f>'By Round'!B39</f>
         <v/>
       </c>
       <c r="D5" s="10">
-        <f>'By Round'!C48</f>
+        <f>'By Round'!C39</f>
         <v/>
       </c>
       <c r="E5" s="10">
-        <f>'By Round'!D48</f>
+        <f>'By Round'!D39</f>
         <v/>
       </c>
       <c r="F5" s="10">
-        <f>IF(ISBLANK('By Round'!F48),"",'By Round'!F48)</f>
+        <f>IF(ISBLANK('By Round'!F39),"",'By Round'!F39)</f>
         <v/>
       </c>
       <c r="G5">
-        <f>IF(ISBLANK('By Round'!G48),"",'By Round'!G48)</f>
+        <f>IF(ISBLANK('By Round'!G39),"",'By Round'!G39)</f>
         <v/>
       </c>
       <c r="H5">
-        <f>IF(ISBLANK('By Round'!H48),"",'By Round'!H48)</f>
+        <f>IF(ISBLANK('By Round'!H39),"",'By Round'!H39)</f>
         <v/>
       </c>
       <c r="I5">
-        <f>IF(ISBLANK('By Round'!I48),"",'By Round'!I48)</f>
+        <f>IF(ISBLANK('By Round'!I39),"",'By Round'!I39)</f>
         <v/>
       </c>
       <c r="J5">
-        <f>IF(ISBLANK('By Round'!J48),"",'By Round'!J48)</f>
+        <f>IF(ISBLANK('By Round'!J39),"",'By Round'!J39)</f>
         <v/>
       </c>
       <c r="K5">
-        <f>IF(ISBLANK('By Round'!K48),"",'By Round'!K48)</f>
+        <f>IF(ISBLANK('By Round'!K39),"",'By Round'!K39)</f>
         <v/>
       </c>
       <c r="L5">
-        <f>IF(ISBLANK('By Round'!L48),"",'By Round'!L48)</f>
+        <f>IF(ISBLANK('By Round'!L39),"",'By Round'!L39)</f>
         <v/>
       </c>
       <c r="M5" s="11">
@@ -1329,47 +1329,47 @@
     <row r="6">
       <c r="A6" s="15" t="n"/>
       <c r="B6" s="16">
-        <f>'By Round'!A75</f>
+        <f>'By Round'!A57</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>'By Round'!B78</f>
+        <f>'By Round'!B60</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>'By Round'!C78</f>
+        <f>'By Round'!C60</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>'By Round'!D78</f>
+        <f>'By Round'!D60</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>IF(ISBLANK('By Round'!F78),"",'By Round'!F78)</f>
+        <f>IF(ISBLANK('By Round'!F60),"",'By Round'!F60)</f>
         <v/>
       </c>
       <c r="G6" s="15">
-        <f>IF(ISBLANK('By Round'!G78),"",'By Round'!G78)</f>
+        <f>IF(ISBLANK('By Round'!G60),"",'By Round'!G60)</f>
         <v/>
       </c>
       <c r="H6" s="15">
-        <f>IF(ISBLANK('By Round'!H78),"",'By Round'!H78)</f>
+        <f>IF(ISBLANK('By Round'!H60),"",'By Round'!H60)</f>
         <v/>
       </c>
       <c r="I6" s="15">
-        <f>IF(ISBLANK('By Round'!I78),"",'By Round'!I78)</f>
+        <f>IF(ISBLANK('By Round'!I60),"",'By Round'!I60)</f>
         <v/>
       </c>
       <c r="J6" s="15">
-        <f>IF(ISBLANK('By Round'!J78),"",'By Round'!J78)</f>
+        <f>IF(ISBLANK('By Round'!J60),"",'By Round'!J60)</f>
         <v/>
       </c>
       <c r="K6" s="15">
-        <f>IF(ISBLANK('By Round'!K78),"",'By Round'!K78)</f>
+        <f>IF(ISBLANK('By Round'!K60),"",'By Round'!K60)</f>
         <v/>
       </c>
       <c r="L6" s="15">
-        <f>IF(ISBLANK('By Round'!L78),"",'By Round'!L78)</f>
+        <f>IF(ISBLANK('By Round'!L60),"",'By Round'!L60)</f>
         <v/>
       </c>
       <c r="M6" s="17">
@@ -1584,47 +1584,47 @@
     </row>
     <row r="8">
       <c r="B8" s="10">
-        <f>'By Round'!A63</f>
+        <f>'By Round'!A48</f>
         <v/>
       </c>
       <c r="C8" s="10">
-        <f>'By Round'!B69</f>
+        <f>'By Round'!B54</f>
         <v/>
       </c>
       <c r="D8" s="10">
-        <f>'By Round'!C69</f>
+        <f>'By Round'!C54</f>
         <v/>
       </c>
       <c r="E8" s="10">
-        <f>'By Round'!D69</f>
+        <f>'By Round'!D54</f>
         <v/>
       </c>
       <c r="F8" s="10">
-        <f>IF(ISBLANK('By Round'!F70),"",'By Round'!F70)</f>
+        <f>IF(ISBLANK('By Round'!F55),"",'By Round'!F55)</f>
         <v/>
       </c>
       <c r="G8">
-        <f>IF(ISBLANK('By Round'!G70),"",'By Round'!G70)</f>
+        <f>IF(ISBLANK('By Round'!G55),"",'By Round'!G55)</f>
         <v/>
       </c>
       <c r="H8">
-        <f>IF(ISBLANK('By Round'!H70),"",'By Round'!H70)</f>
+        <f>IF(ISBLANK('By Round'!H55),"",'By Round'!H55)</f>
         <v/>
       </c>
       <c r="I8">
-        <f>IF(ISBLANK('By Round'!I70),"",'By Round'!I70)</f>
+        <f>IF(ISBLANK('By Round'!I55),"",'By Round'!I55)</f>
         <v/>
       </c>
       <c r="J8">
-        <f>IF(ISBLANK('By Round'!J70),"",'By Round'!J70)</f>
+        <f>IF(ISBLANK('By Round'!J55),"",'By Round'!J55)</f>
         <v/>
       </c>
       <c r="K8">
-        <f>IF(ISBLANK('By Round'!K70),"",'By Round'!K70)</f>
+        <f>IF(ISBLANK('By Round'!K55),"",'By Round'!K55)</f>
         <v/>
       </c>
       <c r="L8">
-        <f>IF(ISBLANK('By Round'!L70),"",'By Round'!L70)</f>
+        <f>IF(ISBLANK('By Round'!L55),"",'By Round'!L55)</f>
         <v/>
       </c>
       <c r="M8" s="11">
@@ -1710,47 +1710,47 @@
     </row>
     <row r="9">
       <c r="B9" s="10">
-        <f>'By Round'!A39</f>
+        <f>'By Round'!A30</f>
         <v/>
       </c>
       <c r="C9" s="10">
-        <f>'By Round'!B48</f>
+        <f>'By Round'!B39</f>
         <v/>
       </c>
       <c r="D9" s="10">
-        <f>'By Round'!C48</f>
+        <f>'By Round'!C39</f>
         <v/>
       </c>
       <c r="E9" s="10">
-        <f>'By Round'!D48</f>
+        <f>'By Round'!D39</f>
         <v/>
       </c>
       <c r="F9" s="10">
-        <f>IF(ISBLANK('By Round'!F49),"",'By Round'!F49)</f>
+        <f>IF(ISBLANK('By Round'!F40),"",'By Round'!F40)</f>
         <v/>
       </c>
       <c r="G9">
-        <f>IF(ISBLANK('By Round'!G49),"",'By Round'!G49)</f>
+        <f>IF(ISBLANK('By Round'!G40),"",'By Round'!G40)</f>
         <v/>
       </c>
       <c r="H9">
-        <f>IF(ISBLANK('By Round'!H49),"",'By Round'!H49)</f>
+        <f>IF(ISBLANK('By Round'!H40),"",'By Round'!H40)</f>
         <v/>
       </c>
       <c r="I9">
-        <f>IF(ISBLANK('By Round'!I49),"",'By Round'!I49)</f>
+        <f>IF(ISBLANK('By Round'!I40),"",'By Round'!I40)</f>
         <v/>
       </c>
       <c r="J9">
-        <f>IF(ISBLANK('By Round'!J49),"",'By Round'!J49)</f>
+        <f>IF(ISBLANK('By Round'!J40),"",'By Round'!J40)</f>
         <v/>
       </c>
       <c r="K9">
-        <f>IF(ISBLANK('By Round'!K49),"",'By Round'!K49)</f>
+        <f>IF(ISBLANK('By Round'!K40),"",'By Round'!K40)</f>
         <v/>
       </c>
       <c r="L9">
-        <f>IF(ISBLANK('By Round'!L49),"",'By Round'!L49)</f>
+        <f>IF(ISBLANK('By Round'!L40),"",'By Round'!L40)</f>
         <v/>
       </c>
       <c r="M9" s="11">
@@ -1837,47 +1837,47 @@
     <row r="10">
       <c r="A10" s="15" t="n"/>
       <c r="B10" s="16">
-        <f>'By Round'!A75</f>
+        <f>'By Round'!A57</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>'By Round'!B78</f>
+        <f>'By Round'!B60</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>'By Round'!C78</f>
+        <f>'By Round'!C60</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>'By Round'!D78</f>
+        <f>'By Round'!D60</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>IF(ISBLANK('By Round'!F79),"",'By Round'!F79)</f>
+        <f>IF(ISBLANK('By Round'!F61),"",'By Round'!F61)</f>
         <v/>
       </c>
       <c r="G10" s="15">
-        <f>IF(ISBLANK('By Round'!G79),"",'By Round'!G79)</f>
+        <f>IF(ISBLANK('By Round'!G61),"",'By Round'!G61)</f>
         <v/>
       </c>
       <c r="H10" s="15">
-        <f>IF(ISBLANK('By Round'!H79),"",'By Round'!H79)</f>
+        <f>IF(ISBLANK('By Round'!H61),"",'By Round'!H61)</f>
         <v/>
       </c>
       <c r="I10" s="15">
-        <f>IF(ISBLANK('By Round'!I79),"",'By Round'!I79)</f>
+        <f>IF(ISBLANK('By Round'!I61),"",'By Round'!I61)</f>
         <v/>
       </c>
       <c r="J10" s="15">
-        <f>IF(ISBLANK('By Round'!J79),"",'By Round'!J79)</f>
+        <f>IF(ISBLANK('By Round'!J61),"",'By Round'!J61)</f>
         <v/>
       </c>
       <c r="K10" s="15">
-        <f>IF(ISBLANK('By Round'!K79),"",'By Round'!K79)</f>
+        <f>IF(ISBLANK('By Round'!K61),"",'By Round'!K61)</f>
         <v/>
       </c>
       <c r="L10" s="15">
-        <f>IF(ISBLANK('By Round'!L79),"",'By Round'!L79)</f>
+        <f>IF(ISBLANK('By Round'!L61),"",'By Round'!L61)</f>
         <v/>
       </c>
       <c r="M10" s="17">
@@ -2092,47 +2092,47 @@
     </row>
     <row r="12">
       <c r="B12" s="10">
-        <f>'By Round'!A63</f>
+        <f>'By Round'!A48</f>
         <v/>
       </c>
       <c r="C12" s="10">
-        <f>'By Round'!B69</f>
+        <f>'By Round'!B54</f>
         <v/>
       </c>
       <c r="D12" s="10">
-        <f>'By Round'!C69</f>
+        <f>'By Round'!C54</f>
         <v/>
       </c>
       <c r="E12" s="10">
-        <f>'By Round'!D69</f>
+        <f>'By Round'!D54</f>
         <v/>
       </c>
       <c r="F12" s="10">
-        <f>IF(ISBLANK('By Round'!F71),"",'By Round'!F71)</f>
+        <f>IF(ISBLANK('By Round'!F56),"",'By Round'!F56)</f>
         <v/>
       </c>
       <c r="G12">
-        <f>IF(ISBLANK('By Round'!G71),"",'By Round'!G71)</f>
+        <f>IF(ISBLANK('By Round'!G56),"",'By Round'!G56)</f>
         <v/>
       </c>
       <c r="H12">
-        <f>IF(ISBLANK('By Round'!H71),"",'By Round'!H71)</f>
+        <f>IF(ISBLANK('By Round'!H56),"",'By Round'!H56)</f>
         <v/>
       </c>
       <c r="I12">
-        <f>IF(ISBLANK('By Round'!I71),"",'By Round'!I71)</f>
+        <f>IF(ISBLANK('By Round'!I56),"",'By Round'!I56)</f>
         <v/>
       </c>
       <c r="J12">
-        <f>IF(ISBLANK('By Round'!J71),"",'By Round'!J71)</f>
+        <f>IF(ISBLANK('By Round'!J56),"",'By Round'!J56)</f>
         <v/>
       </c>
       <c r="K12">
-        <f>IF(ISBLANK('By Round'!K71),"",'By Round'!K71)</f>
+        <f>IF(ISBLANK('By Round'!K56),"",'By Round'!K56)</f>
         <v/>
       </c>
       <c r="L12">
-        <f>IF(ISBLANK('By Round'!L71),"",'By Round'!L71)</f>
+        <f>IF(ISBLANK('By Round'!L56),"",'By Round'!L56)</f>
         <v/>
       </c>
       <c r="M12" s="11">
@@ -2218,47 +2218,47 @@
     </row>
     <row r="13">
       <c r="B13" s="10">
-        <f>'By Round'!A39</f>
+        <f>'By Round'!A30</f>
         <v/>
       </c>
       <c r="C13" s="10">
-        <f>'By Round'!B48</f>
+        <f>'By Round'!B39</f>
         <v/>
       </c>
       <c r="D13" s="10">
-        <f>'By Round'!C48</f>
+        <f>'By Round'!C39</f>
         <v/>
       </c>
       <c r="E13" s="10">
-        <f>'By Round'!D48</f>
+        <f>'By Round'!D39</f>
         <v/>
       </c>
       <c r="F13" s="10">
-        <f>IF(ISBLANK('By Round'!F50),"",'By Round'!F50)</f>
+        <f>IF(ISBLANK('By Round'!F41),"",'By Round'!F41)</f>
         <v/>
       </c>
       <c r="G13">
-        <f>IF(ISBLANK('By Round'!G50),"",'By Round'!G50)</f>
+        <f>IF(ISBLANK('By Round'!G41),"",'By Round'!G41)</f>
         <v/>
       </c>
       <c r="H13">
-        <f>IF(ISBLANK('By Round'!H50),"",'By Round'!H50)</f>
+        <f>IF(ISBLANK('By Round'!H41),"",'By Round'!H41)</f>
         <v/>
       </c>
       <c r="I13">
-        <f>IF(ISBLANK('By Round'!I50),"",'By Round'!I50)</f>
+        <f>IF(ISBLANK('By Round'!I41),"",'By Round'!I41)</f>
         <v/>
       </c>
       <c r="J13">
-        <f>IF(ISBLANK('By Round'!J50),"",'By Round'!J50)</f>
+        <f>IF(ISBLANK('By Round'!J41),"",'By Round'!J41)</f>
         <v/>
       </c>
       <c r="K13">
-        <f>IF(ISBLANK('By Round'!K50),"",'By Round'!K50)</f>
+        <f>IF(ISBLANK('By Round'!K41),"",'By Round'!K41)</f>
         <v/>
       </c>
       <c r="L13">
-        <f>IF(ISBLANK('By Round'!L50),"",'By Round'!L50)</f>
+        <f>IF(ISBLANK('By Round'!L41),"",'By Round'!L41)</f>
         <v/>
       </c>
       <c r="M13" s="11">
@@ -2345,47 +2345,47 @@
     <row r="14">
       <c r="A14" s="15" t="n"/>
       <c r="B14" s="16">
-        <f>'By Round'!A75</f>
+        <f>'By Round'!A57</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>'By Round'!B78</f>
+        <f>'By Round'!B60</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>'By Round'!C78</f>
+        <f>'By Round'!C60</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>'By Round'!D78</f>
+        <f>'By Round'!D60</f>
         <v/>
       </c>
       <c r="F14" s="16">
-        <f>IF(ISBLANK('By Round'!F80),"",'By Round'!F80)</f>
+        <f>IF(ISBLANK('By Round'!F62),"",'By Round'!F62)</f>
         <v/>
       </c>
       <c r="G14" s="15">
-        <f>IF(ISBLANK('By Round'!G80),"",'By Round'!G80)</f>
+        <f>IF(ISBLANK('By Round'!G62),"",'By Round'!G62)</f>
         <v/>
       </c>
       <c r="H14" s="15">
-        <f>IF(ISBLANK('By Round'!H80),"",'By Round'!H80)</f>
+        <f>IF(ISBLANK('By Round'!H62),"",'By Round'!H62)</f>
         <v/>
       </c>
       <c r="I14" s="15">
-        <f>IF(ISBLANK('By Round'!I80),"",'By Round'!I80)</f>
+        <f>IF(ISBLANK('By Round'!I62),"",'By Round'!I62)</f>
         <v/>
       </c>
       <c r="J14" s="15">
-        <f>IF(ISBLANK('By Round'!J80),"",'By Round'!J80)</f>
+        <f>IF(ISBLANK('By Round'!J62),"",'By Round'!J62)</f>
         <v/>
       </c>
       <c r="K14" s="15">
-        <f>IF(ISBLANK('By Round'!K80),"",'By Round'!K80)</f>
+        <f>IF(ISBLANK('By Round'!K62),"",'By Round'!K62)</f>
         <v/>
       </c>
       <c r="L14" s="15">
-        <f>IF(ISBLANK('By Round'!L80),"",'By Round'!L80)</f>
+        <f>IF(ISBLANK('By Round'!L62),"",'By Round'!L62)</f>
         <v/>
       </c>
       <c r="M14" s="17">
@@ -2474,47 +2474,47 @@
         <v>4</v>
       </c>
       <c r="B15" s="10">
-        <f>'By Round'!A15</f>
+        <f>'By Round'!A12</f>
         <v/>
       </c>
       <c r="C15" s="10">
-        <f>'By Round'!B15</f>
+        <f>'By Round'!B12</f>
         <v/>
       </c>
       <c r="D15" s="10">
-        <f>'By Round'!C15</f>
+        <f>'By Round'!C12</f>
         <v/>
       </c>
       <c r="E15" s="10">
-        <f>'By Round'!D15</f>
+        <f>'By Round'!D12</f>
         <v/>
       </c>
       <c r="F15" s="10">
-        <f>IF(ISBLANK('By Round'!F15),"",'By Round'!F15)</f>
+        <f>IF(ISBLANK('By Round'!F12),"",'By Round'!F12)</f>
         <v/>
       </c>
       <c r="G15">
-        <f>IF(ISBLANK('By Round'!G15),"",'By Round'!G15)</f>
+        <f>IF(ISBLANK('By Round'!G12),"",'By Round'!G12)</f>
         <v/>
       </c>
       <c r="H15">
-        <f>IF(ISBLANK('By Round'!H15),"",'By Round'!H15)</f>
+        <f>IF(ISBLANK('By Round'!H12),"",'By Round'!H12)</f>
         <v/>
       </c>
       <c r="I15">
-        <f>IF(ISBLANK('By Round'!I15),"",'By Round'!I15)</f>
+        <f>IF(ISBLANK('By Round'!I12),"",'By Round'!I12)</f>
         <v/>
       </c>
       <c r="J15">
-        <f>IF(ISBLANK('By Round'!J15),"",'By Round'!J15)</f>
+        <f>IF(ISBLANK('By Round'!J12),"",'By Round'!J12)</f>
         <v/>
       </c>
       <c r="K15">
-        <f>IF(ISBLANK('By Round'!K15),"",'By Round'!K15)</f>
+        <f>IF(ISBLANK('By Round'!K12),"",'By Round'!K12)</f>
         <v/>
       </c>
       <c r="L15">
-        <f>IF(ISBLANK('By Round'!L15),"",'By Round'!L15)</f>
+        <f>IF(ISBLANK('By Round'!L12),"",'By Round'!L12)</f>
         <v/>
       </c>
       <c r="M15" s="11">
@@ -2600,47 +2600,47 @@
     </row>
     <row r="16">
       <c r="B16" s="10">
-        <f>'By Round'!A75</f>
+        <f>'By Round'!A57</f>
         <v/>
       </c>
       <c r="C16" s="10">
-        <f>'By Round'!B81</f>
+        <f>'By Round'!B63</f>
         <v/>
       </c>
       <c r="D16" s="10">
-        <f>'By Round'!C81</f>
+        <f>'By Round'!C63</f>
         <v/>
       </c>
       <c r="E16" s="10">
-        <f>'By Round'!D81</f>
+        <f>'By Round'!D63</f>
         <v/>
       </c>
       <c r="F16" s="10">
-        <f>IF(ISBLANK('By Round'!F81),"",'By Round'!F81)</f>
+        <f>IF(ISBLANK('By Round'!F63),"",'By Round'!F63)</f>
         <v/>
       </c>
       <c r="G16">
-        <f>IF(ISBLANK('By Round'!G81),"",'By Round'!G81)</f>
+        <f>IF(ISBLANK('By Round'!G63),"",'By Round'!G63)</f>
         <v/>
       </c>
       <c r="H16">
-        <f>IF(ISBLANK('By Round'!H81),"",'By Round'!H81)</f>
+        <f>IF(ISBLANK('By Round'!H63),"",'By Round'!H63)</f>
         <v/>
       </c>
       <c r="I16">
-        <f>IF(ISBLANK('By Round'!I81),"",'By Round'!I81)</f>
+        <f>IF(ISBLANK('By Round'!I63),"",'By Round'!I63)</f>
         <v/>
       </c>
       <c r="J16">
-        <f>IF(ISBLANK('By Round'!J81),"",'By Round'!J81)</f>
+        <f>IF(ISBLANK('By Round'!J63),"",'By Round'!J63)</f>
         <v/>
       </c>
       <c r="K16">
-        <f>IF(ISBLANK('By Round'!K81),"",'By Round'!K81)</f>
+        <f>IF(ISBLANK('By Round'!K63),"",'By Round'!K63)</f>
         <v/>
       </c>
       <c r="L16">
-        <f>IF(ISBLANK('By Round'!L81),"",'By Round'!L81)</f>
+        <f>IF(ISBLANK('By Round'!L63),"",'By Round'!L63)</f>
         <v/>
       </c>
       <c r="M16" s="11">
@@ -2726,47 +2726,47 @@
     </row>
     <row r="17">
       <c r="B17" s="10">
-        <f>'By Round'!A51</f>
+        <f>'By Round'!A39</f>
         <v/>
       </c>
       <c r="C17" s="10">
-        <f>'By Round'!B60</f>
+        <f>'By Round'!B48</f>
         <v/>
       </c>
       <c r="D17" s="10">
-        <f>'By Round'!C60</f>
+        <f>'By Round'!C48</f>
         <v/>
       </c>
       <c r="E17" s="10">
-        <f>'By Round'!D60</f>
+        <f>'By Round'!D48</f>
         <v/>
       </c>
       <c r="F17" s="10">
-        <f>IF(ISBLANK('By Round'!F60),"",'By Round'!F60)</f>
+        <f>IF(ISBLANK('By Round'!F48),"",'By Round'!F48)</f>
         <v/>
       </c>
       <c r="G17">
-        <f>IF(ISBLANK('By Round'!G60),"",'By Round'!G60)</f>
+        <f>IF(ISBLANK('By Round'!G48),"",'By Round'!G48)</f>
         <v/>
       </c>
       <c r="H17">
-        <f>IF(ISBLANK('By Round'!H60),"",'By Round'!H60)</f>
+        <f>IF(ISBLANK('By Round'!H48),"",'By Round'!H48)</f>
         <v/>
       </c>
       <c r="I17">
-        <f>IF(ISBLANK('By Round'!I60),"",'By Round'!I60)</f>
+        <f>IF(ISBLANK('By Round'!I48),"",'By Round'!I48)</f>
         <v/>
       </c>
       <c r="J17">
-        <f>IF(ISBLANK('By Round'!J60),"",'By Round'!J60)</f>
+        <f>IF(ISBLANK('By Round'!J48),"",'By Round'!J48)</f>
         <v/>
       </c>
       <c r="K17">
-        <f>IF(ISBLANK('By Round'!K60),"",'By Round'!K60)</f>
+        <f>IF(ISBLANK('By Round'!K48),"",'By Round'!K48)</f>
         <v/>
       </c>
       <c r="L17">
-        <f>IF(ISBLANK('By Round'!L60),"",'By Round'!L60)</f>
+        <f>IF(ISBLANK('By Round'!L48),"",'By Round'!L48)</f>
         <v/>
       </c>
       <c r="M17" s="11">
@@ -2982,47 +2982,47 @@
         <v>5</v>
       </c>
       <c r="B19" s="10">
-        <f>'By Round'!A15</f>
+        <f>'By Round'!A12</f>
         <v/>
       </c>
       <c r="C19" s="10">
-        <f>'By Round'!B15</f>
+        <f>'By Round'!B12</f>
         <v/>
       </c>
       <c r="D19" s="10">
-        <f>'By Round'!C15</f>
+        <f>'By Round'!C12</f>
         <v/>
       </c>
       <c r="E19" s="10">
-        <f>'By Round'!D15</f>
+        <f>'By Round'!D12</f>
         <v/>
       </c>
       <c r="F19" s="10">
-        <f>IF(ISBLANK('By Round'!F16),"",'By Round'!F16)</f>
+        <f>IF(ISBLANK('By Round'!F13),"",'By Round'!F13)</f>
         <v/>
       </c>
       <c r="G19">
-        <f>IF(ISBLANK('By Round'!G16),"",'By Round'!G16)</f>
+        <f>IF(ISBLANK('By Round'!G13),"",'By Round'!G13)</f>
         <v/>
       </c>
       <c r="H19">
-        <f>IF(ISBLANK('By Round'!H16),"",'By Round'!H16)</f>
+        <f>IF(ISBLANK('By Round'!H13),"",'By Round'!H13)</f>
         <v/>
       </c>
       <c r="I19">
-        <f>IF(ISBLANK('By Round'!I16),"",'By Round'!I16)</f>
+        <f>IF(ISBLANK('By Round'!I13),"",'By Round'!I13)</f>
         <v/>
       </c>
       <c r="J19">
-        <f>IF(ISBLANK('By Round'!J16),"",'By Round'!J16)</f>
+        <f>IF(ISBLANK('By Round'!J13),"",'By Round'!J13)</f>
         <v/>
       </c>
       <c r="K19">
-        <f>IF(ISBLANK('By Round'!K16),"",'By Round'!K16)</f>
+        <f>IF(ISBLANK('By Round'!K13),"",'By Round'!K13)</f>
         <v/>
       </c>
       <c r="L19">
-        <f>IF(ISBLANK('By Round'!L16),"",'By Round'!L16)</f>
+        <f>IF(ISBLANK('By Round'!L13),"",'By Round'!L13)</f>
         <v/>
       </c>
       <c r="M19" s="11">
@@ -3108,47 +3108,47 @@
     </row>
     <row r="20">
       <c r="B20" s="10">
-        <f>'By Round'!A75</f>
+        <f>'By Round'!A57</f>
         <v/>
       </c>
       <c r="C20" s="10">
-        <f>'By Round'!B81</f>
+        <f>'By Round'!B63</f>
         <v/>
       </c>
       <c r="D20" s="10">
-        <f>'By Round'!C81</f>
+        <f>'By Round'!C63</f>
         <v/>
       </c>
       <c r="E20" s="10">
-        <f>'By Round'!D81</f>
+        <f>'By Round'!D63</f>
         <v/>
       </c>
       <c r="F20" s="10">
-        <f>IF(ISBLANK('By Round'!F82),"",'By Round'!F82)</f>
+        <f>IF(ISBLANK('By Round'!F64),"",'By Round'!F64)</f>
         <v/>
       </c>
       <c r="G20">
-        <f>IF(ISBLANK('By Round'!G82),"",'By Round'!G82)</f>
+        <f>IF(ISBLANK('By Round'!G64),"",'By Round'!G64)</f>
         <v/>
       </c>
       <c r="H20">
-        <f>IF(ISBLANK('By Round'!H82),"",'By Round'!H82)</f>
+        <f>IF(ISBLANK('By Round'!H64),"",'By Round'!H64)</f>
         <v/>
       </c>
       <c r="I20">
-        <f>IF(ISBLANK('By Round'!I82),"",'By Round'!I82)</f>
+        <f>IF(ISBLANK('By Round'!I64),"",'By Round'!I64)</f>
         <v/>
       </c>
       <c r="J20">
-        <f>IF(ISBLANK('By Round'!J82),"",'By Round'!J82)</f>
+        <f>IF(ISBLANK('By Round'!J64),"",'By Round'!J64)</f>
         <v/>
       </c>
       <c r="K20">
-        <f>IF(ISBLANK('By Round'!K82),"",'By Round'!K82)</f>
+        <f>IF(ISBLANK('By Round'!K64),"",'By Round'!K64)</f>
         <v/>
       </c>
       <c r="L20">
-        <f>IF(ISBLANK('By Round'!L82),"",'By Round'!L82)</f>
+        <f>IF(ISBLANK('By Round'!L64),"",'By Round'!L64)</f>
         <v/>
       </c>
       <c r="M20" s="11">
@@ -3234,47 +3234,47 @@
     </row>
     <row r="21">
       <c r="B21" s="10">
-        <f>'By Round'!A51</f>
+        <f>'By Round'!A39</f>
         <v/>
       </c>
       <c r="C21" s="10">
-        <f>'By Round'!B60</f>
+        <f>'By Round'!B48</f>
         <v/>
       </c>
       <c r="D21" s="10">
-        <f>'By Round'!C60</f>
+        <f>'By Round'!C48</f>
         <v/>
       </c>
       <c r="E21" s="10">
-        <f>'By Round'!D60</f>
+        <f>'By Round'!D48</f>
         <v/>
       </c>
       <c r="F21" s="10">
-        <f>IF(ISBLANK('By Round'!F61),"",'By Round'!F61)</f>
+        <f>IF(ISBLANK('By Round'!F49),"",'By Round'!F49)</f>
         <v/>
       </c>
       <c r="G21">
-        <f>IF(ISBLANK('By Round'!G61),"",'By Round'!G61)</f>
+        <f>IF(ISBLANK('By Round'!G49),"",'By Round'!G49)</f>
         <v/>
       </c>
       <c r="H21">
-        <f>IF(ISBLANK('By Round'!H61),"",'By Round'!H61)</f>
+        <f>IF(ISBLANK('By Round'!H49),"",'By Round'!H49)</f>
         <v/>
       </c>
       <c r="I21">
-        <f>IF(ISBLANK('By Round'!I61),"",'By Round'!I61)</f>
+        <f>IF(ISBLANK('By Round'!I49),"",'By Round'!I49)</f>
         <v/>
       </c>
       <c r="J21">
-        <f>IF(ISBLANK('By Round'!J61),"",'By Round'!J61)</f>
+        <f>IF(ISBLANK('By Round'!J49),"",'By Round'!J49)</f>
         <v/>
       </c>
       <c r="K21">
-        <f>IF(ISBLANK('By Round'!K61),"",'By Round'!K61)</f>
+        <f>IF(ISBLANK('By Round'!K49),"",'By Round'!K49)</f>
         <v/>
       </c>
       <c r="L21">
-        <f>IF(ISBLANK('By Round'!L61),"",'By Round'!L61)</f>
+        <f>IF(ISBLANK('By Round'!L49),"",'By Round'!L49)</f>
         <v/>
       </c>
       <c r="M21" s="11">
@@ -3490,47 +3490,47 @@
         <v>6</v>
       </c>
       <c r="B23" s="10">
-        <f>'By Round'!A15</f>
+        <f>'By Round'!A12</f>
         <v/>
       </c>
       <c r="C23" s="10">
-        <f>'By Round'!B15</f>
+        <f>'By Round'!B12</f>
         <v/>
       </c>
       <c r="D23" s="10">
-        <f>'By Round'!C15</f>
+        <f>'By Round'!C12</f>
         <v/>
       </c>
       <c r="E23" s="10">
-        <f>'By Round'!D15</f>
+        <f>'By Round'!D12</f>
         <v/>
       </c>
       <c r="F23" s="10">
-        <f>IF(ISBLANK('By Round'!F17),"",'By Round'!F17)</f>
+        <f>IF(ISBLANK('By Round'!F14),"",'By Round'!F14)</f>
         <v/>
       </c>
       <c r="G23">
-        <f>IF(ISBLANK('By Round'!G17),"",'By Round'!G17)</f>
+        <f>IF(ISBLANK('By Round'!G14),"",'By Round'!G14)</f>
         <v/>
       </c>
       <c r="H23">
-        <f>IF(ISBLANK('By Round'!H17),"",'By Round'!H17)</f>
+        <f>IF(ISBLANK('By Round'!H14),"",'By Round'!H14)</f>
         <v/>
       </c>
       <c r="I23">
-        <f>IF(ISBLANK('By Round'!I17),"",'By Round'!I17)</f>
+        <f>IF(ISBLANK('By Round'!I14),"",'By Round'!I14)</f>
         <v/>
       </c>
       <c r="J23">
-        <f>IF(ISBLANK('By Round'!J17),"",'By Round'!J17)</f>
+        <f>IF(ISBLANK('By Round'!J14),"",'By Round'!J14)</f>
         <v/>
       </c>
       <c r="K23">
-        <f>IF(ISBLANK('By Round'!K17),"",'By Round'!K17)</f>
+        <f>IF(ISBLANK('By Round'!K14),"",'By Round'!K14)</f>
         <v/>
       </c>
       <c r="L23">
-        <f>IF(ISBLANK('By Round'!L17),"",'By Round'!L17)</f>
+        <f>IF(ISBLANK('By Round'!L14),"",'By Round'!L14)</f>
         <v/>
       </c>
       <c r="M23" s="11">
@@ -3616,47 +3616,47 @@
     </row>
     <row r="24">
       <c r="B24" s="10">
-        <f>'By Round'!A75</f>
+        <f>'By Round'!A57</f>
         <v/>
       </c>
       <c r="C24" s="10">
-        <f>'By Round'!B81</f>
+        <f>'By Round'!B63</f>
         <v/>
       </c>
       <c r="D24" s="10">
-        <f>'By Round'!C81</f>
+        <f>'By Round'!C63</f>
         <v/>
       </c>
       <c r="E24" s="10">
-        <f>'By Round'!D81</f>
+        <f>'By Round'!D63</f>
         <v/>
       </c>
       <c r="F24" s="10">
-        <f>IF(ISBLANK('By Round'!F83),"",'By Round'!F83)</f>
+        <f>IF(ISBLANK('By Round'!F65),"",'By Round'!F65)</f>
         <v/>
       </c>
       <c r="G24">
-        <f>IF(ISBLANK('By Round'!G83),"",'By Round'!G83)</f>
+        <f>IF(ISBLANK('By Round'!G65),"",'By Round'!G65)</f>
         <v/>
       </c>
       <c r="H24">
-        <f>IF(ISBLANK('By Round'!H83),"",'By Round'!H83)</f>
+        <f>IF(ISBLANK('By Round'!H65),"",'By Round'!H65)</f>
         <v/>
       </c>
       <c r="I24">
-        <f>IF(ISBLANK('By Round'!I83),"",'By Round'!I83)</f>
+        <f>IF(ISBLANK('By Round'!I65),"",'By Round'!I65)</f>
         <v/>
       </c>
       <c r="J24">
-        <f>IF(ISBLANK('By Round'!J83),"",'By Round'!J83)</f>
+        <f>IF(ISBLANK('By Round'!J65),"",'By Round'!J65)</f>
         <v/>
       </c>
       <c r="K24">
-        <f>IF(ISBLANK('By Round'!K83),"",'By Round'!K83)</f>
+        <f>IF(ISBLANK('By Round'!K65),"",'By Round'!K65)</f>
         <v/>
       </c>
       <c r="L24">
-        <f>IF(ISBLANK('By Round'!L83),"",'By Round'!L83)</f>
+        <f>IF(ISBLANK('By Round'!L65),"",'By Round'!L65)</f>
         <v/>
       </c>
       <c r="M24" s="11">
@@ -3742,47 +3742,47 @@
     </row>
     <row r="25">
       <c r="B25" s="10">
-        <f>'By Round'!A51</f>
+        <f>'By Round'!A39</f>
         <v/>
       </c>
       <c r="C25" s="10">
-        <f>'By Round'!B60</f>
+        <f>'By Round'!B48</f>
         <v/>
       </c>
       <c r="D25" s="10">
-        <f>'By Round'!C60</f>
+        <f>'By Round'!C48</f>
         <v/>
       </c>
       <c r="E25" s="10">
-        <f>'By Round'!D60</f>
+        <f>'By Round'!D48</f>
         <v/>
       </c>
       <c r="F25" s="10">
-        <f>IF(ISBLANK('By Round'!F62),"",'By Round'!F62)</f>
+        <f>IF(ISBLANK('By Round'!F50),"",'By Round'!F50)</f>
         <v/>
       </c>
       <c r="G25">
-        <f>IF(ISBLANK('By Round'!G62),"",'By Round'!G62)</f>
+        <f>IF(ISBLANK('By Round'!G50),"",'By Round'!G50)</f>
         <v/>
       </c>
       <c r="H25">
-        <f>IF(ISBLANK('By Round'!H62),"",'By Round'!H62)</f>
+        <f>IF(ISBLANK('By Round'!H50),"",'By Round'!H50)</f>
         <v/>
       </c>
       <c r="I25">
-        <f>IF(ISBLANK('By Round'!I62),"",'By Round'!I62)</f>
+        <f>IF(ISBLANK('By Round'!I50),"",'By Round'!I50)</f>
         <v/>
       </c>
       <c r="J25">
-        <f>IF(ISBLANK('By Round'!J62),"",'By Round'!J62)</f>
+        <f>IF(ISBLANK('By Round'!J50),"",'By Round'!J50)</f>
         <v/>
       </c>
       <c r="K25">
-        <f>IF(ISBLANK('By Round'!K62),"",'By Round'!K62)</f>
+        <f>IF(ISBLANK('By Round'!K50),"",'By Round'!K50)</f>
         <v/>
       </c>
       <c r="L25">
-        <f>IF(ISBLANK('By Round'!L62),"",'By Round'!L62)</f>
+        <f>IF(ISBLANK('By Round'!L50),"",'By Round'!L50)</f>
         <v/>
       </c>
       <c r="M25" s="11">
@@ -3998,47 +3998,47 @@
         <v>7</v>
       </c>
       <c r="B27" s="10">
-        <f>'By Round'!A27</f>
+        <f>'By Round'!A21</f>
         <v/>
       </c>
       <c r="C27" s="10">
-        <f>'By Round'!B27</f>
+        <f>'By Round'!B21</f>
         <v/>
       </c>
       <c r="D27" s="10">
-        <f>'By Round'!C27</f>
+        <f>'By Round'!C21</f>
         <v/>
       </c>
       <c r="E27" s="10">
-        <f>'By Round'!D27</f>
+        <f>'By Round'!D21</f>
         <v/>
       </c>
       <c r="F27" s="10">
-        <f>IF(ISBLANK('By Round'!F27),"",'By Round'!F27)</f>
+        <f>IF(ISBLANK('By Round'!F21),"",'By Round'!F21)</f>
         <v/>
       </c>
       <c r="G27">
-        <f>IF(ISBLANK('By Round'!G27),"",'By Round'!G27)</f>
+        <f>IF(ISBLANK('By Round'!G21),"",'By Round'!G21)</f>
         <v/>
       </c>
       <c r="H27">
-        <f>IF(ISBLANK('By Round'!H27),"",'By Round'!H27)</f>
+        <f>IF(ISBLANK('By Round'!H21),"",'By Round'!H21)</f>
         <v/>
       </c>
       <c r="I27">
-        <f>IF(ISBLANK('By Round'!I27),"",'By Round'!I27)</f>
+        <f>IF(ISBLANK('By Round'!I21),"",'By Round'!I21)</f>
         <v/>
       </c>
       <c r="J27">
-        <f>IF(ISBLANK('By Round'!J27),"",'By Round'!J27)</f>
+        <f>IF(ISBLANK('By Round'!J21),"",'By Round'!J21)</f>
         <v/>
       </c>
       <c r="K27">
-        <f>IF(ISBLANK('By Round'!K27),"",'By Round'!K27)</f>
+        <f>IF(ISBLANK('By Round'!K21),"",'By Round'!K21)</f>
         <v/>
       </c>
       <c r="L27">
-        <f>IF(ISBLANK('By Round'!L27),"",'By Round'!L27)</f>
+        <f>IF(ISBLANK('By Round'!L21),"",'By Round'!L21)</f>
         <v/>
       </c>
       <c r="M27" s="11">
@@ -4250,47 +4250,47 @@
     </row>
     <row r="29">
       <c r="B29" s="10">
-        <f>'By Round'!A63</f>
+        <f>'By Round'!A48</f>
         <v/>
       </c>
       <c r="C29" s="10">
-        <f>'By Round'!B72</f>
+        <f>'By Round'!B57</f>
         <v/>
       </c>
       <c r="D29" s="10">
-        <f>'By Round'!C72</f>
+        <f>'By Round'!C57</f>
         <v/>
       </c>
       <c r="E29" s="10">
-        <f>'By Round'!D72</f>
+        <f>'By Round'!D57</f>
         <v/>
       </c>
       <c r="F29" s="10">
-        <f>IF(ISBLANK('By Round'!F72),"",'By Round'!F72)</f>
+        <f>IF(ISBLANK('By Round'!F57),"",'By Round'!F57)</f>
         <v/>
       </c>
       <c r="G29">
-        <f>IF(ISBLANK('By Round'!G72),"",'By Round'!G72)</f>
+        <f>IF(ISBLANK('By Round'!G57),"",'By Round'!G57)</f>
         <v/>
       </c>
       <c r="H29">
-        <f>IF(ISBLANK('By Round'!H72),"",'By Round'!H72)</f>
+        <f>IF(ISBLANK('By Round'!H57),"",'By Round'!H57)</f>
         <v/>
       </c>
       <c r="I29">
-        <f>IF(ISBLANK('By Round'!I72),"",'By Round'!I72)</f>
+        <f>IF(ISBLANK('By Round'!I57),"",'By Round'!I57)</f>
         <v/>
       </c>
       <c r="J29">
-        <f>IF(ISBLANK('By Round'!J72),"",'By Round'!J72)</f>
+        <f>IF(ISBLANK('By Round'!J57),"",'By Round'!J57)</f>
         <v/>
       </c>
       <c r="K29">
-        <f>IF(ISBLANK('By Round'!K72),"",'By Round'!K72)</f>
+        <f>IF(ISBLANK('By Round'!K57),"",'By Round'!K57)</f>
         <v/>
       </c>
       <c r="L29">
-        <f>IF(ISBLANK('By Round'!L72),"",'By Round'!L72)</f>
+        <f>IF(ISBLANK('By Round'!L57),"",'By Round'!L57)</f>
         <v/>
       </c>
       <c r="M29" s="11">
@@ -4377,47 +4377,47 @@
     <row r="30">
       <c r="A30" s="15" t="n"/>
       <c r="B30" s="16">
-        <f>'By Round'!A15</f>
+        <f>'By Round'!A12</f>
         <v/>
       </c>
       <c r="C30" s="16">
-        <f>'By Round'!B18</f>
+        <f>'By Round'!B15</f>
         <v/>
       </c>
       <c r="D30" s="16">
-        <f>'By Round'!C18</f>
+        <f>'By Round'!C15</f>
         <v/>
       </c>
       <c r="E30" s="16">
-        <f>'By Round'!D18</f>
+        <f>'By Round'!D15</f>
         <v/>
       </c>
       <c r="F30" s="16">
-        <f>IF(ISBLANK('By Round'!F18),"",'By Round'!F18)</f>
+        <f>IF(ISBLANK('By Round'!F15),"",'By Round'!F15)</f>
         <v/>
       </c>
       <c r="G30" s="15">
-        <f>IF(ISBLANK('By Round'!G18),"",'By Round'!G18)</f>
+        <f>IF(ISBLANK('By Round'!G15),"",'By Round'!G15)</f>
         <v/>
       </c>
       <c r="H30" s="15">
-        <f>IF(ISBLANK('By Round'!H18),"",'By Round'!H18)</f>
+        <f>IF(ISBLANK('By Round'!H15),"",'By Round'!H15)</f>
         <v/>
       </c>
       <c r="I30" s="15">
-        <f>IF(ISBLANK('By Round'!I18),"",'By Round'!I18)</f>
+        <f>IF(ISBLANK('By Round'!I15),"",'By Round'!I15)</f>
         <v/>
       </c>
       <c r="J30" s="15">
-        <f>IF(ISBLANK('By Round'!J18),"",'By Round'!J18)</f>
+        <f>IF(ISBLANK('By Round'!J15),"",'By Round'!J15)</f>
         <v/>
       </c>
       <c r="K30" s="15">
-        <f>IF(ISBLANK('By Round'!K18),"",'By Round'!K18)</f>
+        <f>IF(ISBLANK('By Round'!K15),"",'By Round'!K15)</f>
         <v/>
       </c>
       <c r="L30" s="15">
-        <f>IF(ISBLANK('By Round'!L18),"",'By Round'!L18)</f>
+        <f>IF(ISBLANK('By Round'!L15),"",'By Round'!L15)</f>
         <v/>
       </c>
       <c r="M30" s="17">
@@ -4506,47 +4506,47 @@
         <v>8</v>
       </c>
       <c r="B31" s="10">
-        <f>'By Round'!A27</f>
+        <f>'By Round'!A21</f>
         <v/>
       </c>
       <c r="C31" s="10">
-        <f>'By Round'!B27</f>
+        <f>'By Round'!B21</f>
         <v/>
       </c>
       <c r="D31" s="10">
-        <f>'By Round'!C27</f>
+        <f>'By Round'!C21</f>
         <v/>
       </c>
       <c r="E31" s="10">
-        <f>'By Round'!D27</f>
+        <f>'By Round'!D21</f>
         <v/>
       </c>
       <c r="F31" s="10">
-        <f>IF(ISBLANK('By Round'!F28),"",'By Round'!F28)</f>
+        <f>IF(ISBLANK('By Round'!F22),"",'By Round'!F22)</f>
         <v/>
       </c>
       <c r="G31">
-        <f>IF(ISBLANK('By Round'!G28),"",'By Round'!G28)</f>
+        <f>IF(ISBLANK('By Round'!G22),"",'By Round'!G22)</f>
         <v/>
       </c>
       <c r="H31">
-        <f>IF(ISBLANK('By Round'!H28),"",'By Round'!H28)</f>
+        <f>IF(ISBLANK('By Round'!H22),"",'By Round'!H22)</f>
         <v/>
       </c>
       <c r="I31">
-        <f>IF(ISBLANK('By Round'!I28),"",'By Round'!I28)</f>
+        <f>IF(ISBLANK('By Round'!I22),"",'By Round'!I22)</f>
         <v/>
       </c>
       <c r="J31">
-        <f>IF(ISBLANK('By Round'!J28),"",'By Round'!J28)</f>
+        <f>IF(ISBLANK('By Round'!J22),"",'By Round'!J22)</f>
         <v/>
       </c>
       <c r="K31">
-        <f>IF(ISBLANK('By Round'!K28),"",'By Round'!K28)</f>
+        <f>IF(ISBLANK('By Round'!K22),"",'By Round'!K22)</f>
         <v/>
       </c>
       <c r="L31">
-        <f>IF(ISBLANK('By Round'!L28),"",'By Round'!L28)</f>
+        <f>IF(ISBLANK('By Round'!L22),"",'By Round'!L22)</f>
         <v/>
       </c>
       <c r="M31" s="11">
@@ -4758,47 +4758,47 @@
     </row>
     <row r="33">
       <c r="B33" s="10">
-        <f>'By Round'!A63</f>
+        <f>'By Round'!A48</f>
         <v/>
       </c>
       <c r="C33" s="10">
-        <f>'By Round'!B72</f>
+        <f>'By Round'!B57</f>
         <v/>
       </c>
       <c r="D33" s="10">
-        <f>'By Round'!C72</f>
+        <f>'By Round'!C57</f>
         <v/>
       </c>
       <c r="E33" s="10">
-        <f>'By Round'!D72</f>
+        <f>'By Round'!D57</f>
         <v/>
       </c>
       <c r="F33" s="10">
-        <f>IF(ISBLANK('By Round'!F73),"",'By Round'!F73)</f>
+        <f>IF(ISBLANK('By Round'!F58),"",'By Round'!F58)</f>
         <v/>
       </c>
       <c r="G33">
-        <f>IF(ISBLANK('By Round'!G73),"",'By Round'!G73)</f>
+        <f>IF(ISBLANK('By Round'!G58),"",'By Round'!G58)</f>
         <v/>
       </c>
       <c r="H33">
-        <f>IF(ISBLANK('By Round'!H73),"",'By Round'!H73)</f>
+        <f>IF(ISBLANK('By Round'!H58),"",'By Round'!H58)</f>
         <v/>
       </c>
       <c r="I33">
-        <f>IF(ISBLANK('By Round'!I73),"",'By Round'!I73)</f>
+        <f>IF(ISBLANK('By Round'!I58),"",'By Round'!I58)</f>
         <v/>
       </c>
       <c r="J33">
-        <f>IF(ISBLANK('By Round'!J73),"",'By Round'!J73)</f>
+        <f>IF(ISBLANK('By Round'!J58),"",'By Round'!J58)</f>
         <v/>
       </c>
       <c r="K33">
-        <f>IF(ISBLANK('By Round'!K73),"",'By Round'!K73)</f>
+        <f>IF(ISBLANK('By Round'!K58),"",'By Round'!K58)</f>
         <v/>
       </c>
       <c r="L33">
-        <f>IF(ISBLANK('By Round'!L73),"",'By Round'!L73)</f>
+        <f>IF(ISBLANK('By Round'!L58),"",'By Round'!L58)</f>
         <v/>
       </c>
       <c r="M33" s="11">
@@ -4885,47 +4885,47 @@
     <row r="34">
       <c r="A34" s="15" t="n"/>
       <c r="B34" s="16">
-        <f>'By Round'!A15</f>
+        <f>'By Round'!A12</f>
         <v/>
       </c>
       <c r="C34" s="16">
-        <f>'By Round'!B18</f>
+        <f>'By Round'!B15</f>
         <v/>
       </c>
       <c r="D34" s="16">
-        <f>'By Round'!C18</f>
+        <f>'By Round'!C15</f>
         <v/>
       </c>
       <c r="E34" s="16">
-        <f>'By Round'!D18</f>
+        <f>'By Round'!D15</f>
         <v/>
       </c>
       <c r="F34" s="16">
-        <f>IF(ISBLANK('By Round'!F19),"",'By Round'!F19)</f>
+        <f>IF(ISBLANK('By Round'!F16),"",'By Round'!F16)</f>
         <v/>
       </c>
       <c r="G34" s="15">
-        <f>IF(ISBLANK('By Round'!G19),"",'By Round'!G19)</f>
+        <f>IF(ISBLANK('By Round'!G16),"",'By Round'!G16)</f>
         <v/>
       </c>
       <c r="H34" s="15">
-        <f>IF(ISBLANK('By Round'!H19),"",'By Round'!H19)</f>
+        <f>IF(ISBLANK('By Round'!H16),"",'By Round'!H16)</f>
         <v/>
       </c>
       <c r="I34" s="15">
-        <f>IF(ISBLANK('By Round'!I19),"",'By Round'!I19)</f>
+        <f>IF(ISBLANK('By Round'!I16),"",'By Round'!I16)</f>
         <v/>
       </c>
       <c r="J34" s="15">
-        <f>IF(ISBLANK('By Round'!J19),"",'By Round'!J19)</f>
+        <f>IF(ISBLANK('By Round'!J16),"",'By Round'!J16)</f>
         <v/>
       </c>
       <c r="K34" s="15">
-        <f>IF(ISBLANK('By Round'!K19),"",'By Round'!K19)</f>
+        <f>IF(ISBLANK('By Round'!K16),"",'By Round'!K16)</f>
         <v/>
       </c>
       <c r="L34" s="15">
-        <f>IF(ISBLANK('By Round'!L19),"",'By Round'!L19)</f>
+        <f>IF(ISBLANK('By Round'!L16),"",'By Round'!L16)</f>
         <v/>
       </c>
       <c r="M34" s="17">
@@ -5014,47 +5014,47 @@
         <v>9</v>
       </c>
       <c r="B35" s="10">
-        <f>'By Round'!A27</f>
+        <f>'By Round'!A21</f>
         <v/>
       </c>
       <c r="C35" s="10">
-        <f>'By Round'!B27</f>
+        <f>'By Round'!B21</f>
         <v/>
       </c>
       <c r="D35" s="10">
-        <f>'By Round'!C27</f>
+        <f>'By Round'!C21</f>
         <v/>
       </c>
       <c r="E35" s="10">
-        <f>'By Round'!D27</f>
+        <f>'By Round'!D21</f>
         <v/>
       </c>
       <c r="F35" s="10">
-        <f>IF(ISBLANK('By Round'!F29),"",'By Round'!F29)</f>
+        <f>IF(ISBLANK('By Round'!F23),"",'By Round'!F23)</f>
         <v/>
       </c>
       <c r="G35">
-        <f>IF(ISBLANK('By Round'!G29),"",'By Round'!G29)</f>
+        <f>IF(ISBLANK('By Round'!G23),"",'By Round'!G23)</f>
         <v/>
       </c>
       <c r="H35">
-        <f>IF(ISBLANK('By Round'!H29),"",'By Round'!H29)</f>
+        <f>IF(ISBLANK('By Round'!H23),"",'By Round'!H23)</f>
         <v/>
       </c>
       <c r="I35">
-        <f>IF(ISBLANK('By Round'!I29),"",'By Round'!I29)</f>
+        <f>IF(ISBLANK('By Round'!I23),"",'By Round'!I23)</f>
         <v/>
       </c>
       <c r="J35">
-        <f>IF(ISBLANK('By Round'!J29),"",'By Round'!J29)</f>
+        <f>IF(ISBLANK('By Round'!J23),"",'By Round'!J23)</f>
         <v/>
       </c>
       <c r="K35">
-        <f>IF(ISBLANK('By Round'!K29),"",'By Round'!K29)</f>
+        <f>IF(ISBLANK('By Round'!K23),"",'By Round'!K23)</f>
         <v/>
       </c>
       <c r="L35">
-        <f>IF(ISBLANK('By Round'!L29),"",'By Round'!L29)</f>
+        <f>IF(ISBLANK('By Round'!L23),"",'By Round'!L23)</f>
         <v/>
       </c>
       <c r="M35" s="11">
@@ -5266,47 +5266,47 @@
     </row>
     <row r="37">
       <c r="B37" s="10">
-        <f>'By Round'!A63</f>
+        <f>'By Round'!A48</f>
         <v/>
       </c>
       <c r="C37" s="10">
-        <f>'By Round'!B72</f>
+        <f>'By Round'!B57</f>
         <v/>
       </c>
       <c r="D37" s="10">
-        <f>'By Round'!C72</f>
+        <f>'By Round'!C57</f>
         <v/>
       </c>
       <c r="E37" s="10">
-        <f>'By Round'!D72</f>
+        <f>'By Round'!D57</f>
         <v/>
       </c>
       <c r="F37" s="10">
-        <f>IF(ISBLANK('By Round'!F74),"",'By Round'!F74)</f>
+        <f>IF(ISBLANK('By Round'!F59),"",'By Round'!F59)</f>
         <v/>
       </c>
       <c r="G37">
-        <f>IF(ISBLANK('By Round'!G74),"",'By Round'!G74)</f>
+        <f>IF(ISBLANK('By Round'!G59),"",'By Round'!G59)</f>
         <v/>
       </c>
       <c r="H37">
-        <f>IF(ISBLANK('By Round'!H74),"",'By Round'!H74)</f>
+        <f>IF(ISBLANK('By Round'!H59),"",'By Round'!H59)</f>
         <v/>
       </c>
       <c r="I37">
-        <f>IF(ISBLANK('By Round'!I74),"",'By Round'!I74)</f>
+        <f>IF(ISBLANK('By Round'!I59),"",'By Round'!I59)</f>
         <v/>
       </c>
       <c r="J37">
-        <f>IF(ISBLANK('By Round'!J74),"",'By Round'!J74)</f>
+        <f>IF(ISBLANK('By Round'!J59),"",'By Round'!J59)</f>
         <v/>
       </c>
       <c r="K37">
-        <f>IF(ISBLANK('By Round'!K74),"",'By Round'!K74)</f>
+        <f>IF(ISBLANK('By Round'!K59),"",'By Round'!K59)</f>
         <v/>
       </c>
       <c r="L37">
-        <f>IF(ISBLANK('By Round'!L74),"",'By Round'!L74)</f>
+        <f>IF(ISBLANK('By Round'!L59),"",'By Round'!L59)</f>
         <v/>
       </c>
       <c r="M37" s="11">
@@ -5393,47 +5393,47 @@
     <row r="38">
       <c r="A38" s="15" t="n"/>
       <c r="B38" s="16">
-        <f>'By Round'!A15</f>
+        <f>'By Round'!A12</f>
         <v/>
       </c>
       <c r="C38" s="16">
-        <f>'By Round'!B18</f>
+        <f>'By Round'!B15</f>
         <v/>
       </c>
       <c r="D38" s="16">
-        <f>'By Round'!C18</f>
+        <f>'By Round'!C15</f>
         <v/>
       </c>
       <c r="E38" s="16">
-        <f>'By Round'!D18</f>
+        <f>'By Round'!D15</f>
         <v/>
       </c>
       <c r="F38" s="16">
-        <f>IF(ISBLANK('By Round'!F20),"",'By Round'!F20)</f>
+        <f>IF(ISBLANK('By Round'!F17),"",'By Round'!F17)</f>
         <v/>
       </c>
       <c r="G38" s="15">
-        <f>IF(ISBLANK('By Round'!G20),"",'By Round'!G20)</f>
+        <f>IF(ISBLANK('By Round'!G17),"",'By Round'!G17)</f>
         <v/>
       </c>
       <c r="H38" s="15">
-        <f>IF(ISBLANK('By Round'!H20),"",'By Round'!H20)</f>
+        <f>IF(ISBLANK('By Round'!H17),"",'By Round'!H17)</f>
         <v/>
       </c>
       <c r="I38" s="15">
-        <f>IF(ISBLANK('By Round'!I20),"",'By Round'!I20)</f>
+        <f>IF(ISBLANK('By Round'!I17),"",'By Round'!I17)</f>
         <v/>
       </c>
       <c r="J38" s="15">
-        <f>IF(ISBLANK('By Round'!J20),"",'By Round'!J20)</f>
+        <f>IF(ISBLANK('By Round'!J17),"",'By Round'!J17)</f>
         <v/>
       </c>
       <c r="K38" s="15">
-        <f>IF(ISBLANK('By Round'!K20),"",'By Round'!K20)</f>
+        <f>IF(ISBLANK('By Round'!K17),"",'By Round'!K17)</f>
         <v/>
       </c>
       <c r="L38" s="15">
-        <f>IF(ISBLANK('By Round'!L20),"",'By Round'!L20)</f>
+        <f>IF(ISBLANK('By Round'!L17),"",'By Round'!L17)</f>
         <v/>
       </c>
       <c r="M38" s="17">
@@ -5522,47 +5522,47 @@
         <v>10</v>
       </c>
       <c r="B39" s="10">
-        <f>'By Round'!A39</f>
+        <f>'By Round'!A30</f>
         <v/>
       </c>
       <c r="C39" s="10">
-        <f>'By Round'!B39</f>
+        <f>'By Round'!B30</f>
         <v/>
       </c>
       <c r="D39" s="10">
-        <f>'By Round'!C39</f>
+        <f>'By Round'!C30</f>
         <v/>
       </c>
       <c r="E39" s="10">
-        <f>'By Round'!D39</f>
+        <f>'By Round'!D30</f>
         <v/>
       </c>
       <c r="F39" s="10">
-        <f>IF(ISBLANK('By Round'!F39),"",'By Round'!F39)</f>
+        <f>IF(ISBLANK('By Round'!F30),"",'By Round'!F30)</f>
         <v/>
       </c>
       <c r="G39">
-        <f>IF(ISBLANK('By Round'!G39),"",'By Round'!G39)</f>
+        <f>IF(ISBLANK('By Round'!G30),"",'By Round'!G30)</f>
         <v/>
       </c>
       <c r="H39">
-        <f>IF(ISBLANK('By Round'!H39),"",'By Round'!H39)</f>
+        <f>IF(ISBLANK('By Round'!H30),"",'By Round'!H30)</f>
         <v/>
       </c>
       <c r="I39">
-        <f>IF(ISBLANK('By Round'!I39),"",'By Round'!I39)</f>
+        <f>IF(ISBLANK('By Round'!I30),"",'By Round'!I30)</f>
         <v/>
       </c>
       <c r="J39">
-        <f>IF(ISBLANK('By Round'!J39),"",'By Round'!J39)</f>
+        <f>IF(ISBLANK('By Round'!J30),"",'By Round'!J30)</f>
         <v/>
       </c>
       <c r="K39">
-        <f>IF(ISBLANK('By Round'!K39),"",'By Round'!K39)</f>
+        <f>IF(ISBLANK('By Round'!K30),"",'By Round'!K30)</f>
         <v/>
       </c>
       <c r="L39">
-        <f>IF(ISBLANK('By Round'!L39),"",'By Round'!L39)</f>
+        <f>IF(ISBLANK('By Round'!L30),"",'By Round'!L30)</f>
         <v/>
       </c>
       <c r="M39" s="11">
@@ -5648,47 +5648,47 @@
     </row>
     <row r="40">
       <c r="B40" s="10">
-        <f>'By Round'!A27</f>
+        <f>'By Round'!A21</f>
         <v/>
       </c>
       <c r="C40" s="10">
-        <f>'By Round'!B30</f>
+        <f>'By Round'!B24</f>
         <v/>
       </c>
       <c r="D40" s="10">
-        <f>'By Round'!C30</f>
+        <f>'By Round'!C24</f>
         <v/>
       </c>
       <c r="E40" s="10">
-        <f>'By Round'!D30</f>
+        <f>'By Round'!D24</f>
         <v/>
       </c>
       <c r="F40" s="10">
-        <f>IF(ISBLANK('By Round'!F30),"",'By Round'!F30)</f>
+        <f>IF(ISBLANK('By Round'!F24),"",'By Round'!F24)</f>
         <v/>
       </c>
       <c r="G40">
-        <f>IF(ISBLANK('By Round'!G30),"",'By Round'!G30)</f>
+        <f>IF(ISBLANK('By Round'!G24),"",'By Round'!G24)</f>
         <v/>
       </c>
       <c r="H40">
-        <f>IF(ISBLANK('By Round'!H30),"",'By Round'!H30)</f>
+        <f>IF(ISBLANK('By Round'!H24),"",'By Round'!H24)</f>
         <v/>
       </c>
       <c r="I40">
-        <f>IF(ISBLANK('By Round'!I30),"",'By Round'!I30)</f>
+        <f>IF(ISBLANK('By Round'!I24),"",'By Round'!I24)</f>
         <v/>
       </c>
       <c r="J40">
-        <f>IF(ISBLANK('By Round'!J30),"",'By Round'!J30)</f>
+        <f>IF(ISBLANK('By Round'!J24),"",'By Round'!J24)</f>
         <v/>
       </c>
       <c r="K40">
-        <f>IF(ISBLANK('By Round'!K30),"",'By Round'!K30)</f>
+        <f>IF(ISBLANK('By Round'!K24),"",'By Round'!K24)</f>
         <v/>
       </c>
       <c r="L40">
-        <f>IF(ISBLANK('By Round'!L30),"",'By Round'!L30)</f>
+        <f>IF(ISBLANK('By Round'!L24),"",'By Round'!L24)</f>
         <v/>
       </c>
       <c r="M40" s="11">
@@ -5774,47 +5774,47 @@
     </row>
     <row r="41">
       <c r="B41" s="10">
-        <f>'By Round'!A15</f>
+        <f>'By Round'!A12</f>
         <v/>
       </c>
       <c r="C41" s="10">
-        <f>'By Round'!B21</f>
+        <f>'By Round'!B18</f>
         <v/>
       </c>
       <c r="D41" s="10">
-        <f>'By Round'!C21</f>
+        <f>'By Round'!C18</f>
         <v/>
       </c>
       <c r="E41" s="10">
-        <f>'By Round'!D21</f>
+        <f>'By Round'!D18</f>
         <v/>
       </c>
       <c r="F41" s="10">
-        <f>IF(ISBLANK('By Round'!F21),"",'By Round'!F21)</f>
+        <f>IF(ISBLANK('By Round'!F18),"",'By Round'!F18)</f>
         <v/>
       </c>
       <c r="G41">
-        <f>IF(ISBLANK('By Round'!G21),"",'By Round'!G21)</f>
+        <f>IF(ISBLANK('By Round'!G18),"",'By Round'!G18)</f>
         <v/>
       </c>
       <c r="H41">
-        <f>IF(ISBLANK('By Round'!H21),"",'By Round'!H21)</f>
+        <f>IF(ISBLANK('By Round'!H18),"",'By Round'!H18)</f>
         <v/>
       </c>
       <c r="I41">
-        <f>IF(ISBLANK('By Round'!I21),"",'By Round'!I21)</f>
+        <f>IF(ISBLANK('By Round'!I18),"",'By Round'!I18)</f>
         <v/>
       </c>
       <c r="J41">
-        <f>IF(ISBLANK('By Round'!J21),"",'By Round'!J21)</f>
+        <f>IF(ISBLANK('By Round'!J18),"",'By Round'!J18)</f>
         <v/>
       </c>
       <c r="K41">
-        <f>IF(ISBLANK('By Round'!K21),"",'By Round'!K21)</f>
+        <f>IF(ISBLANK('By Round'!K18),"",'By Round'!K18)</f>
         <v/>
       </c>
       <c r="L41">
-        <f>IF(ISBLANK('By Round'!L21),"",'By Round'!L21)</f>
+        <f>IF(ISBLANK('By Round'!L18),"",'By Round'!L18)</f>
         <v/>
       </c>
       <c r="M41" s="11">
@@ -5901,47 +5901,47 @@
     <row r="42">
       <c r="A42" s="15" t="n"/>
       <c r="B42" s="16">
-        <f>'By Round'!A75</f>
+        <f>'By Round'!A57</f>
         <v/>
       </c>
       <c r="C42" s="16">
-        <f>'By Round'!B84</f>
+        <f>'By Round'!B66</f>
         <v/>
       </c>
       <c r="D42" s="16">
-        <f>'By Round'!C84</f>
+        <f>'By Round'!C66</f>
         <v/>
       </c>
       <c r="E42" s="16">
-        <f>'By Round'!D84</f>
+        <f>'By Round'!D66</f>
         <v/>
       </c>
       <c r="F42" s="16">
-        <f>IF(ISBLANK('By Round'!F84),"",'By Round'!F84)</f>
+        <f>IF(ISBLANK('By Round'!F66),"",'By Round'!F66)</f>
         <v/>
       </c>
       <c r="G42" s="15">
-        <f>IF(ISBLANK('By Round'!G84),"",'By Round'!G84)</f>
+        <f>IF(ISBLANK('By Round'!G66),"",'By Round'!G66)</f>
         <v/>
       </c>
       <c r="H42" s="15">
-        <f>IF(ISBLANK('By Round'!H84),"",'By Round'!H84)</f>
+        <f>IF(ISBLANK('By Round'!H66),"",'By Round'!H66)</f>
         <v/>
       </c>
       <c r="I42" s="15">
-        <f>IF(ISBLANK('By Round'!I84),"",'By Round'!I84)</f>
+        <f>IF(ISBLANK('By Round'!I66),"",'By Round'!I66)</f>
         <v/>
       </c>
       <c r="J42" s="15">
-        <f>IF(ISBLANK('By Round'!J84),"",'By Round'!J84)</f>
+        <f>IF(ISBLANK('By Round'!J66),"",'By Round'!J66)</f>
         <v/>
       </c>
       <c r="K42" s="15">
-        <f>IF(ISBLANK('By Round'!K84),"",'By Round'!K84)</f>
+        <f>IF(ISBLANK('By Round'!K66),"",'By Round'!K66)</f>
         <v/>
       </c>
       <c r="L42" s="15">
-        <f>IF(ISBLANK('By Round'!L84),"",'By Round'!L84)</f>
+        <f>IF(ISBLANK('By Round'!L66),"",'By Round'!L66)</f>
         <v/>
       </c>
       <c r="M42" s="17">
@@ -6030,47 +6030,47 @@
         <v>11</v>
       </c>
       <c r="B43" s="10">
-        <f>'By Round'!A39</f>
+        <f>'By Round'!A30</f>
         <v/>
       </c>
       <c r="C43" s="10">
-        <f>'By Round'!B39</f>
+        <f>'By Round'!B30</f>
         <v/>
       </c>
       <c r="D43" s="10">
-        <f>'By Round'!C39</f>
+        <f>'By Round'!C30</f>
         <v/>
       </c>
       <c r="E43" s="10">
-        <f>'By Round'!D39</f>
+        <f>'By Round'!D30</f>
         <v/>
       </c>
       <c r="F43" s="10">
-        <f>IF(ISBLANK('By Round'!F40),"",'By Round'!F40)</f>
+        <f>IF(ISBLANK('By Round'!F31),"",'By Round'!F31)</f>
         <v/>
       </c>
       <c r="G43">
-        <f>IF(ISBLANK('By Round'!G40),"",'By Round'!G40)</f>
+        <f>IF(ISBLANK('By Round'!G31),"",'By Round'!G31)</f>
         <v/>
       </c>
       <c r="H43">
-        <f>IF(ISBLANK('By Round'!H40),"",'By Round'!H40)</f>
+        <f>IF(ISBLANK('By Round'!H31),"",'By Round'!H31)</f>
         <v/>
       </c>
       <c r="I43">
-        <f>IF(ISBLANK('By Round'!I40),"",'By Round'!I40)</f>
+        <f>IF(ISBLANK('By Round'!I31),"",'By Round'!I31)</f>
         <v/>
       </c>
       <c r="J43">
-        <f>IF(ISBLANK('By Round'!J40),"",'By Round'!J40)</f>
+        <f>IF(ISBLANK('By Round'!J31),"",'By Round'!J31)</f>
         <v/>
       </c>
       <c r="K43">
-        <f>IF(ISBLANK('By Round'!K40),"",'By Round'!K40)</f>
+        <f>IF(ISBLANK('By Round'!K31),"",'By Round'!K31)</f>
         <v/>
       </c>
       <c r="L43">
-        <f>IF(ISBLANK('By Round'!L40),"",'By Round'!L40)</f>
+        <f>IF(ISBLANK('By Round'!L31),"",'By Round'!L31)</f>
         <v/>
       </c>
       <c r="M43" s="11">
@@ -6156,47 +6156,47 @@
     </row>
     <row r="44">
       <c r="B44" s="10">
-        <f>'By Round'!A27</f>
+        <f>'By Round'!A21</f>
         <v/>
       </c>
       <c r="C44" s="10">
-        <f>'By Round'!B30</f>
+        <f>'By Round'!B24</f>
         <v/>
       </c>
       <c r="D44" s="10">
-        <f>'By Round'!C30</f>
+        <f>'By Round'!C24</f>
         <v/>
       </c>
       <c r="E44" s="10">
-        <f>'By Round'!D30</f>
+        <f>'By Round'!D24</f>
         <v/>
       </c>
       <c r="F44" s="10">
-        <f>IF(ISBLANK('By Round'!F31),"",'By Round'!F31)</f>
+        <f>IF(ISBLANK('By Round'!F25),"",'By Round'!F25)</f>
         <v/>
       </c>
       <c r="G44">
-        <f>IF(ISBLANK('By Round'!G31),"",'By Round'!G31)</f>
+        <f>IF(ISBLANK('By Round'!G25),"",'By Round'!G25)</f>
         <v/>
       </c>
       <c r="H44">
-        <f>IF(ISBLANK('By Round'!H31),"",'By Round'!H31)</f>
+        <f>IF(ISBLANK('By Round'!H25),"",'By Round'!H25)</f>
         <v/>
       </c>
       <c r="I44">
-        <f>IF(ISBLANK('By Round'!I31),"",'By Round'!I31)</f>
+        <f>IF(ISBLANK('By Round'!I25),"",'By Round'!I25)</f>
         <v/>
       </c>
       <c r="J44">
-        <f>IF(ISBLANK('By Round'!J31),"",'By Round'!J31)</f>
+        <f>IF(ISBLANK('By Round'!J25),"",'By Round'!J25)</f>
         <v/>
       </c>
       <c r="K44">
-        <f>IF(ISBLANK('By Round'!K31),"",'By Round'!K31)</f>
+        <f>IF(ISBLANK('By Round'!K25),"",'By Round'!K25)</f>
         <v/>
       </c>
       <c r="L44">
-        <f>IF(ISBLANK('By Round'!L31),"",'By Round'!L31)</f>
+        <f>IF(ISBLANK('By Round'!L25),"",'By Round'!L25)</f>
         <v/>
       </c>
       <c r="M44" s="11">
@@ -6282,47 +6282,47 @@
     </row>
     <row r="45">
       <c r="B45" s="10">
-        <f>'By Round'!A15</f>
+        <f>'By Round'!A12</f>
         <v/>
       </c>
       <c r="C45" s="10">
-        <f>'By Round'!B21</f>
+        <f>'By Round'!B18</f>
         <v/>
       </c>
       <c r="D45" s="10">
-        <f>'By Round'!C21</f>
+        <f>'By Round'!C18</f>
         <v/>
       </c>
       <c r="E45" s="10">
-        <f>'By Round'!D21</f>
+        <f>'By Round'!D18</f>
         <v/>
       </c>
       <c r="F45" s="10">
-        <f>IF(ISBLANK('By Round'!F22),"",'By Round'!F22)</f>
+        <f>IF(ISBLANK('By Round'!F19),"",'By Round'!F19)</f>
         <v/>
       </c>
       <c r="G45">
-        <f>IF(ISBLANK('By Round'!G22),"",'By Round'!G22)</f>
+        <f>IF(ISBLANK('By Round'!G19),"",'By Round'!G19)</f>
         <v/>
       </c>
       <c r="H45">
-        <f>IF(ISBLANK('By Round'!H22),"",'By Round'!H22)</f>
+        <f>IF(ISBLANK('By Round'!H19),"",'By Round'!H19)</f>
         <v/>
       </c>
       <c r="I45">
-        <f>IF(ISBLANK('By Round'!I22),"",'By Round'!I22)</f>
+        <f>IF(ISBLANK('By Round'!I19),"",'By Round'!I19)</f>
         <v/>
       </c>
       <c r="J45">
-        <f>IF(ISBLANK('By Round'!J22),"",'By Round'!J22)</f>
+        <f>IF(ISBLANK('By Round'!J19),"",'By Round'!J19)</f>
         <v/>
       </c>
       <c r="K45">
-        <f>IF(ISBLANK('By Round'!K22),"",'By Round'!K22)</f>
+        <f>IF(ISBLANK('By Round'!K19),"",'By Round'!K19)</f>
         <v/>
       </c>
       <c r="L45">
-        <f>IF(ISBLANK('By Round'!L22),"",'By Round'!L22)</f>
+        <f>IF(ISBLANK('By Round'!L19),"",'By Round'!L19)</f>
         <v/>
       </c>
       <c r="M45" s="11">
@@ -6409,47 +6409,47 @@
     <row r="46">
       <c r="A46" s="15" t="n"/>
       <c r="B46" s="16">
-        <f>'By Round'!A75</f>
+        <f>'By Round'!A57</f>
         <v/>
       </c>
       <c r="C46" s="16">
-        <f>'By Round'!B84</f>
+        <f>'By Round'!B66</f>
         <v/>
       </c>
       <c r="D46" s="16">
-        <f>'By Round'!C84</f>
+        <f>'By Round'!C66</f>
         <v/>
       </c>
       <c r="E46" s="16">
-        <f>'By Round'!D84</f>
+        <f>'By Round'!D66</f>
         <v/>
       </c>
       <c r="F46" s="16">
-        <f>IF(ISBLANK('By Round'!F85),"",'By Round'!F85)</f>
+        <f>IF(ISBLANK('By Round'!F67),"",'By Round'!F67)</f>
         <v/>
       </c>
       <c r="G46" s="15">
-        <f>IF(ISBLANK('By Round'!G85),"",'By Round'!G85)</f>
+        <f>IF(ISBLANK('By Round'!G67),"",'By Round'!G67)</f>
         <v/>
       </c>
       <c r="H46" s="15">
-        <f>IF(ISBLANK('By Round'!H85),"",'By Round'!H85)</f>
+        <f>IF(ISBLANK('By Round'!H67),"",'By Round'!H67)</f>
         <v/>
       </c>
       <c r="I46" s="15">
-        <f>IF(ISBLANK('By Round'!I85),"",'By Round'!I85)</f>
+        <f>IF(ISBLANK('By Round'!I67),"",'By Round'!I67)</f>
         <v/>
       </c>
       <c r="J46" s="15">
-        <f>IF(ISBLANK('By Round'!J85),"",'By Round'!J85)</f>
+        <f>IF(ISBLANK('By Round'!J67),"",'By Round'!J67)</f>
         <v/>
       </c>
       <c r="K46" s="15">
-        <f>IF(ISBLANK('By Round'!K85),"",'By Round'!K85)</f>
+        <f>IF(ISBLANK('By Round'!K67),"",'By Round'!K67)</f>
         <v/>
       </c>
       <c r="L46" s="15">
-        <f>IF(ISBLANK('By Round'!L85),"",'By Round'!L85)</f>
+        <f>IF(ISBLANK('By Round'!L67),"",'By Round'!L67)</f>
         <v/>
       </c>
       <c r="M46" s="17">
@@ -6538,47 +6538,47 @@
         <v>12</v>
       </c>
       <c r="B47" s="10">
-        <f>'By Round'!A39</f>
+        <f>'By Round'!A30</f>
         <v/>
       </c>
       <c r="C47" s="10">
-        <f>'By Round'!B39</f>
+        <f>'By Round'!B30</f>
         <v/>
       </c>
       <c r="D47" s="10">
-        <f>'By Round'!C39</f>
+        <f>'By Round'!C30</f>
         <v/>
       </c>
       <c r="E47" s="10">
-        <f>'By Round'!D39</f>
+        <f>'By Round'!D30</f>
         <v/>
       </c>
       <c r="F47" s="10">
-        <f>IF(ISBLANK('By Round'!F41),"",'By Round'!F41)</f>
+        <f>IF(ISBLANK('By Round'!F32),"",'By Round'!F32)</f>
         <v/>
       </c>
       <c r="G47">
-        <f>IF(ISBLANK('By Round'!G41),"",'By Round'!G41)</f>
+        <f>IF(ISBLANK('By Round'!G32),"",'By Round'!G32)</f>
         <v/>
       </c>
       <c r="H47">
-        <f>IF(ISBLANK('By Round'!H41),"",'By Round'!H41)</f>
+        <f>IF(ISBLANK('By Round'!H32),"",'By Round'!H32)</f>
         <v/>
       </c>
       <c r="I47">
-        <f>IF(ISBLANK('By Round'!I41),"",'By Round'!I41)</f>
+        <f>IF(ISBLANK('By Round'!I32),"",'By Round'!I32)</f>
         <v/>
       </c>
       <c r="J47">
-        <f>IF(ISBLANK('By Round'!J41),"",'By Round'!J41)</f>
+        <f>IF(ISBLANK('By Round'!J32),"",'By Round'!J32)</f>
         <v/>
       </c>
       <c r="K47">
-        <f>IF(ISBLANK('By Round'!K41),"",'By Round'!K41)</f>
+        <f>IF(ISBLANK('By Round'!K32),"",'By Round'!K32)</f>
         <v/>
       </c>
       <c r="L47">
-        <f>IF(ISBLANK('By Round'!L41),"",'By Round'!L41)</f>
+        <f>IF(ISBLANK('By Round'!L32),"",'By Round'!L32)</f>
         <v/>
       </c>
       <c r="M47" s="11">
@@ -6664,47 +6664,47 @@
     </row>
     <row r="48">
       <c r="B48" s="10">
-        <f>'By Round'!A27</f>
+        <f>'By Round'!A21</f>
         <v/>
       </c>
       <c r="C48" s="10">
-        <f>'By Round'!B30</f>
+        <f>'By Round'!B24</f>
         <v/>
       </c>
       <c r="D48" s="10">
-        <f>'By Round'!C30</f>
+        <f>'By Round'!C24</f>
         <v/>
       </c>
       <c r="E48" s="10">
-        <f>'By Round'!D30</f>
+        <f>'By Round'!D24</f>
         <v/>
       </c>
       <c r="F48" s="10">
-        <f>IF(ISBLANK('By Round'!F32),"",'By Round'!F32)</f>
+        <f>IF(ISBLANK('By Round'!F26),"",'By Round'!F26)</f>
         <v/>
       </c>
       <c r="G48">
-        <f>IF(ISBLANK('By Round'!G32),"",'By Round'!G32)</f>
+        <f>IF(ISBLANK('By Round'!G26),"",'By Round'!G26)</f>
         <v/>
       </c>
       <c r="H48">
-        <f>IF(ISBLANK('By Round'!H32),"",'By Round'!H32)</f>
+        <f>IF(ISBLANK('By Round'!H26),"",'By Round'!H26)</f>
         <v/>
       </c>
       <c r="I48">
-        <f>IF(ISBLANK('By Round'!I32),"",'By Round'!I32)</f>
+        <f>IF(ISBLANK('By Round'!I26),"",'By Round'!I26)</f>
         <v/>
       </c>
       <c r="J48">
-        <f>IF(ISBLANK('By Round'!J32),"",'By Round'!J32)</f>
+        <f>IF(ISBLANK('By Round'!J26),"",'By Round'!J26)</f>
         <v/>
       </c>
       <c r="K48">
-        <f>IF(ISBLANK('By Round'!K32),"",'By Round'!K32)</f>
+        <f>IF(ISBLANK('By Round'!K26),"",'By Round'!K26)</f>
         <v/>
       </c>
       <c r="L48">
-        <f>IF(ISBLANK('By Round'!L32),"",'By Round'!L32)</f>
+        <f>IF(ISBLANK('By Round'!L26),"",'By Round'!L26)</f>
         <v/>
       </c>
       <c r="M48" s="11">
@@ -6790,47 +6790,47 @@
     </row>
     <row r="49">
       <c r="B49" s="10">
-        <f>'By Round'!A15</f>
+        <f>'By Round'!A12</f>
         <v/>
       </c>
       <c r="C49" s="10">
-        <f>'By Round'!B21</f>
+        <f>'By Round'!B18</f>
         <v/>
       </c>
       <c r="D49" s="10">
-        <f>'By Round'!C21</f>
+        <f>'By Round'!C18</f>
         <v/>
       </c>
       <c r="E49" s="10">
-        <f>'By Round'!D21</f>
+        <f>'By Round'!D18</f>
         <v/>
       </c>
       <c r="F49" s="10">
-        <f>IF(ISBLANK('By Round'!F23),"",'By Round'!F23)</f>
+        <f>IF(ISBLANK('By Round'!F20),"",'By Round'!F20)</f>
         <v/>
       </c>
       <c r="G49">
-        <f>IF(ISBLANK('By Round'!G23),"",'By Round'!G23)</f>
+        <f>IF(ISBLANK('By Round'!G20),"",'By Round'!G20)</f>
         <v/>
       </c>
       <c r="H49">
-        <f>IF(ISBLANK('By Round'!H23),"",'By Round'!H23)</f>
+        <f>IF(ISBLANK('By Round'!H20),"",'By Round'!H20)</f>
         <v/>
       </c>
       <c r="I49">
-        <f>IF(ISBLANK('By Round'!I23),"",'By Round'!I23)</f>
+        <f>IF(ISBLANK('By Round'!I20),"",'By Round'!I20)</f>
         <v/>
       </c>
       <c r="J49">
-        <f>IF(ISBLANK('By Round'!J23),"",'By Round'!J23)</f>
+        <f>IF(ISBLANK('By Round'!J20),"",'By Round'!J20)</f>
         <v/>
       </c>
       <c r="K49">
-        <f>IF(ISBLANK('By Round'!K23),"",'By Round'!K23)</f>
+        <f>IF(ISBLANK('By Round'!K20),"",'By Round'!K20)</f>
         <v/>
       </c>
       <c r="L49">
-        <f>IF(ISBLANK('By Round'!L23),"",'By Round'!L23)</f>
+        <f>IF(ISBLANK('By Round'!L20),"",'By Round'!L20)</f>
         <v/>
       </c>
       <c r="M49" s="11">
@@ -6917,47 +6917,47 @@
     <row r="50">
       <c r="A50" s="15" t="n"/>
       <c r="B50" s="16">
-        <f>'By Round'!A75</f>
+        <f>'By Round'!A57</f>
         <v/>
       </c>
       <c r="C50" s="16">
-        <f>'By Round'!B84</f>
+        <f>'By Round'!B66</f>
         <v/>
       </c>
       <c r="D50" s="16">
-        <f>'By Round'!C84</f>
+        <f>'By Round'!C66</f>
         <v/>
       </c>
       <c r="E50" s="16">
-        <f>'By Round'!D84</f>
+        <f>'By Round'!D66</f>
         <v/>
       </c>
       <c r="F50" s="16">
-        <f>IF(ISBLANK('By Round'!F86),"",'By Round'!F86)</f>
+        <f>IF(ISBLANK('By Round'!F68),"",'By Round'!F68)</f>
         <v/>
       </c>
       <c r="G50" s="15">
-        <f>IF(ISBLANK('By Round'!G86),"",'By Round'!G86)</f>
+        <f>IF(ISBLANK('By Round'!G68),"",'By Round'!G68)</f>
         <v/>
       </c>
       <c r="H50" s="15">
-        <f>IF(ISBLANK('By Round'!H86),"",'By Round'!H86)</f>
+        <f>IF(ISBLANK('By Round'!H68),"",'By Round'!H68)</f>
         <v/>
       </c>
       <c r="I50" s="15">
-        <f>IF(ISBLANK('By Round'!I86),"",'By Round'!I86)</f>
+        <f>IF(ISBLANK('By Round'!I68),"",'By Round'!I68)</f>
         <v/>
       </c>
       <c r="J50" s="15">
-        <f>IF(ISBLANK('By Round'!J86),"",'By Round'!J86)</f>
+        <f>IF(ISBLANK('By Round'!J68),"",'By Round'!J68)</f>
         <v/>
       </c>
       <c r="K50" s="15">
-        <f>IF(ISBLANK('By Round'!K86),"",'By Round'!K86)</f>
+        <f>IF(ISBLANK('By Round'!K68),"",'By Round'!K68)</f>
         <v/>
       </c>
       <c r="L50" s="15">
-        <f>IF(ISBLANK('By Round'!L86),"",'By Round'!L86)</f>
+        <f>IF(ISBLANK('By Round'!L68),"",'By Round'!L68)</f>
         <v/>
       </c>
       <c r="M50" s="17">
@@ -7046,47 +7046,47 @@
         <v>13</v>
       </c>
       <c r="B51" s="10">
-        <f>'By Round'!A51</f>
+        <f>'By Round'!A39</f>
         <v/>
       </c>
       <c r="C51" s="10">
-        <f>'By Round'!B51</f>
+        <f>'By Round'!B39</f>
         <v/>
       </c>
       <c r="D51" s="10">
-        <f>'By Round'!C51</f>
+        <f>'By Round'!C39</f>
         <v/>
       </c>
       <c r="E51" s="10">
-        <f>'By Round'!D51</f>
+        <f>'By Round'!D39</f>
         <v/>
       </c>
       <c r="F51" s="10">
-        <f>IF(ISBLANK('By Round'!F51),"",'By Round'!F51)</f>
+        <f>IF(ISBLANK('By Round'!F39),"",'By Round'!F39)</f>
         <v/>
       </c>
       <c r="G51">
-        <f>IF(ISBLANK('By Round'!G51),"",'By Round'!G51)</f>
+        <f>IF(ISBLANK('By Round'!G39),"",'By Round'!G39)</f>
         <v/>
       </c>
       <c r="H51">
-        <f>IF(ISBLANK('By Round'!H51),"",'By Round'!H51)</f>
+        <f>IF(ISBLANK('By Round'!H39),"",'By Round'!H39)</f>
         <v/>
       </c>
       <c r="I51">
-        <f>IF(ISBLANK('By Round'!I51),"",'By Round'!I51)</f>
+        <f>IF(ISBLANK('By Round'!I39),"",'By Round'!I39)</f>
         <v/>
       </c>
       <c r="J51">
-        <f>IF(ISBLANK('By Round'!J51),"",'By Round'!J51)</f>
+        <f>IF(ISBLANK('By Round'!J39),"",'By Round'!J39)</f>
         <v/>
       </c>
       <c r="K51">
-        <f>IF(ISBLANK('By Round'!K51),"",'By Round'!K51)</f>
+        <f>IF(ISBLANK('By Round'!K39),"",'By Round'!K39)</f>
         <v/>
       </c>
       <c r="L51">
-        <f>IF(ISBLANK('By Round'!L51),"",'By Round'!L51)</f>
+        <f>IF(ISBLANK('By Round'!L39),"",'By Round'!L39)</f>
         <v/>
       </c>
       <c r="M51" s="11">
@@ -7172,47 +7172,47 @@
     </row>
     <row r="52">
       <c r="B52" s="10">
-        <f>'By Round'!A39</f>
+        <f>'By Round'!A30</f>
         <v/>
       </c>
       <c r="C52" s="10">
-        <f>'By Round'!B42</f>
+        <f>'By Round'!B33</f>
         <v/>
       </c>
       <c r="D52" s="10">
-        <f>'By Round'!C42</f>
+        <f>'By Round'!C33</f>
         <v/>
       </c>
       <c r="E52" s="10">
-        <f>'By Round'!D42</f>
+        <f>'By Round'!D33</f>
         <v/>
       </c>
       <c r="F52" s="10">
-        <f>IF(ISBLANK('By Round'!F42),"",'By Round'!F42)</f>
+        <f>IF(ISBLANK('By Round'!F33),"",'By Round'!F33)</f>
         <v/>
       </c>
       <c r="G52">
-        <f>IF(ISBLANK('By Round'!G42),"",'By Round'!G42)</f>
+        <f>IF(ISBLANK('By Round'!G33),"",'By Round'!G33)</f>
         <v/>
       </c>
       <c r="H52">
-        <f>IF(ISBLANK('By Round'!H42),"",'By Round'!H42)</f>
+        <f>IF(ISBLANK('By Round'!H33),"",'By Round'!H33)</f>
         <v/>
       </c>
       <c r="I52">
-        <f>IF(ISBLANK('By Round'!I42),"",'By Round'!I42)</f>
+        <f>IF(ISBLANK('By Round'!I33),"",'By Round'!I33)</f>
         <v/>
       </c>
       <c r="J52">
-        <f>IF(ISBLANK('By Round'!J42),"",'By Round'!J42)</f>
+        <f>IF(ISBLANK('By Round'!J33),"",'By Round'!J33)</f>
         <v/>
       </c>
       <c r="K52">
-        <f>IF(ISBLANK('By Round'!K42),"",'By Round'!K42)</f>
+        <f>IF(ISBLANK('By Round'!K33),"",'By Round'!K33)</f>
         <v/>
       </c>
       <c r="L52">
-        <f>IF(ISBLANK('By Round'!L42),"",'By Round'!L42)</f>
+        <f>IF(ISBLANK('By Round'!L33),"",'By Round'!L33)</f>
         <v/>
       </c>
       <c r="M52" s="11">
@@ -7298,47 +7298,47 @@
     </row>
     <row r="53">
       <c r="B53" s="10">
-        <f>'By Round'!A27</f>
+        <f>'By Round'!A21</f>
         <v/>
       </c>
       <c r="C53" s="10">
-        <f>'By Round'!B33</f>
+        <f>'By Round'!B27</f>
         <v/>
       </c>
       <c r="D53" s="10">
-        <f>'By Round'!C33</f>
+        <f>'By Round'!C27</f>
         <v/>
       </c>
       <c r="E53" s="10">
-        <f>'By Round'!D33</f>
+        <f>'By Round'!D27</f>
         <v/>
       </c>
       <c r="F53" s="10">
-        <f>IF(ISBLANK('By Round'!F33),"",'By Round'!F33)</f>
+        <f>IF(ISBLANK('By Round'!F27),"",'By Round'!F27)</f>
         <v/>
       </c>
       <c r="G53">
-        <f>IF(ISBLANK('By Round'!G33),"",'By Round'!G33)</f>
+        <f>IF(ISBLANK('By Round'!G27),"",'By Round'!G27)</f>
         <v/>
       </c>
       <c r="H53">
-        <f>IF(ISBLANK('By Round'!H33),"",'By Round'!H33)</f>
+        <f>IF(ISBLANK('By Round'!H27),"",'By Round'!H27)</f>
         <v/>
       </c>
       <c r="I53">
-        <f>IF(ISBLANK('By Round'!I33),"",'By Round'!I33)</f>
+        <f>IF(ISBLANK('By Round'!I27),"",'By Round'!I27)</f>
         <v/>
       </c>
       <c r="J53">
-        <f>IF(ISBLANK('By Round'!J33),"",'By Round'!J33)</f>
+        <f>IF(ISBLANK('By Round'!J27),"",'By Round'!J27)</f>
         <v/>
       </c>
       <c r="K53">
-        <f>IF(ISBLANK('By Round'!K33),"",'By Round'!K33)</f>
+        <f>IF(ISBLANK('By Round'!K27),"",'By Round'!K27)</f>
         <v/>
       </c>
       <c r="L53">
-        <f>IF(ISBLANK('By Round'!L33),"",'By Round'!L33)</f>
+        <f>IF(ISBLANK('By Round'!L27),"",'By Round'!L27)</f>
         <v/>
       </c>
       <c r="M53" s="11">
@@ -7554,47 +7554,47 @@
         <v>14</v>
       </c>
       <c r="B55" s="10">
-        <f>'By Round'!A51</f>
+        <f>'By Round'!A39</f>
         <v/>
       </c>
       <c r="C55" s="10">
-        <f>'By Round'!B51</f>
+        <f>'By Round'!B39</f>
         <v/>
       </c>
       <c r="D55" s="10">
-        <f>'By Round'!C51</f>
+        <f>'By Round'!C39</f>
         <v/>
       </c>
       <c r="E55" s="10">
-        <f>'By Round'!D51</f>
+        <f>'By Round'!D39</f>
         <v/>
       </c>
       <c r="F55" s="10">
-        <f>IF(ISBLANK('By Round'!F52),"",'By Round'!F52)</f>
+        <f>IF(ISBLANK('By Round'!F40),"",'By Round'!F40)</f>
         <v/>
       </c>
       <c r="G55">
-        <f>IF(ISBLANK('By Round'!G52),"",'By Round'!G52)</f>
+        <f>IF(ISBLANK('By Round'!G40),"",'By Round'!G40)</f>
         <v/>
       </c>
       <c r="H55">
-        <f>IF(ISBLANK('By Round'!H52),"",'By Round'!H52)</f>
+        <f>IF(ISBLANK('By Round'!H40),"",'By Round'!H40)</f>
         <v/>
       </c>
       <c r="I55">
-        <f>IF(ISBLANK('By Round'!I52),"",'By Round'!I52)</f>
+        <f>IF(ISBLANK('By Round'!I40),"",'By Round'!I40)</f>
         <v/>
       </c>
       <c r="J55">
-        <f>IF(ISBLANK('By Round'!J52),"",'By Round'!J52)</f>
+        <f>IF(ISBLANK('By Round'!J40),"",'By Round'!J40)</f>
         <v/>
       </c>
       <c r="K55">
-        <f>IF(ISBLANK('By Round'!K52),"",'By Round'!K52)</f>
+        <f>IF(ISBLANK('By Round'!K40),"",'By Round'!K40)</f>
         <v/>
       </c>
       <c r="L55">
-        <f>IF(ISBLANK('By Round'!L52),"",'By Round'!L52)</f>
+        <f>IF(ISBLANK('By Round'!L40),"",'By Round'!L40)</f>
         <v/>
       </c>
       <c r="M55" s="11">
@@ -7680,47 +7680,47 @@
     </row>
     <row r="56">
       <c r="B56" s="10">
-        <f>'By Round'!A39</f>
+        <f>'By Round'!A30</f>
         <v/>
       </c>
       <c r="C56" s="10">
-        <f>'By Round'!B42</f>
+        <f>'By Round'!B33</f>
         <v/>
       </c>
       <c r="D56" s="10">
-        <f>'By Round'!C42</f>
+        <f>'By Round'!C33</f>
         <v/>
       </c>
       <c r="E56" s="10">
-        <f>'By Round'!D42</f>
+        <f>'By Round'!D33</f>
         <v/>
       </c>
       <c r="F56" s="10">
-        <f>IF(ISBLANK('By Round'!F43),"",'By Round'!F43)</f>
+        <f>IF(ISBLANK('By Round'!F34),"",'By Round'!F34)</f>
         <v/>
       </c>
       <c r="G56">
-        <f>IF(ISBLANK('By Round'!G43),"",'By Round'!G43)</f>
+        <f>IF(ISBLANK('By Round'!G34),"",'By Round'!G34)</f>
         <v/>
       </c>
       <c r="H56">
-        <f>IF(ISBLANK('By Round'!H43),"",'By Round'!H43)</f>
+        <f>IF(ISBLANK('By Round'!H34),"",'By Round'!H34)</f>
         <v/>
       </c>
       <c r="I56">
-        <f>IF(ISBLANK('By Round'!I43),"",'By Round'!I43)</f>
+        <f>IF(ISBLANK('By Round'!I34),"",'By Round'!I34)</f>
         <v/>
       </c>
       <c r="J56">
-        <f>IF(ISBLANK('By Round'!J43),"",'By Round'!J43)</f>
+        <f>IF(ISBLANK('By Round'!J34),"",'By Round'!J34)</f>
         <v/>
       </c>
       <c r="K56">
-        <f>IF(ISBLANK('By Round'!K43),"",'By Round'!K43)</f>
+        <f>IF(ISBLANK('By Round'!K34),"",'By Round'!K34)</f>
         <v/>
       </c>
       <c r="L56">
-        <f>IF(ISBLANK('By Round'!L43),"",'By Round'!L43)</f>
+        <f>IF(ISBLANK('By Round'!L34),"",'By Round'!L34)</f>
         <v/>
       </c>
       <c r="M56" s="11">
@@ -7806,47 +7806,47 @@
     </row>
     <row r="57">
       <c r="B57" s="10">
-        <f>'By Round'!A27</f>
+        <f>'By Round'!A21</f>
         <v/>
       </c>
       <c r="C57" s="10">
-        <f>'By Round'!B33</f>
+        <f>'By Round'!B27</f>
         <v/>
       </c>
       <c r="D57" s="10">
-        <f>'By Round'!C33</f>
+        <f>'By Round'!C27</f>
         <v/>
       </c>
       <c r="E57" s="10">
-        <f>'By Round'!D33</f>
+        <f>'By Round'!D27</f>
         <v/>
       </c>
       <c r="F57" s="10">
-        <f>IF(ISBLANK('By Round'!F34),"",'By Round'!F34)</f>
+        <f>IF(ISBLANK('By Round'!F28),"",'By Round'!F28)</f>
         <v/>
       </c>
       <c r="G57">
-        <f>IF(ISBLANK('By Round'!G34),"",'By Round'!G34)</f>
+        <f>IF(ISBLANK('By Round'!G28),"",'By Round'!G28)</f>
         <v/>
       </c>
       <c r="H57">
-        <f>IF(ISBLANK('By Round'!H34),"",'By Round'!H34)</f>
+        <f>IF(ISBLANK('By Round'!H28),"",'By Round'!H28)</f>
         <v/>
       </c>
       <c r="I57">
-        <f>IF(ISBLANK('By Round'!I34),"",'By Round'!I34)</f>
+        <f>IF(ISBLANK('By Round'!I28),"",'By Round'!I28)</f>
         <v/>
       </c>
       <c r="J57">
-        <f>IF(ISBLANK('By Round'!J34),"",'By Round'!J34)</f>
+        <f>IF(ISBLANK('By Round'!J28),"",'By Round'!J28)</f>
         <v/>
       </c>
       <c r="K57">
-        <f>IF(ISBLANK('By Round'!K34),"",'By Round'!K34)</f>
+        <f>IF(ISBLANK('By Round'!K28),"",'By Round'!K28)</f>
         <v/>
       </c>
       <c r="L57">
-        <f>IF(ISBLANK('By Round'!L34),"",'By Round'!L34)</f>
+        <f>IF(ISBLANK('By Round'!L28),"",'By Round'!L28)</f>
         <v/>
       </c>
       <c r="M57" s="11">
@@ -8062,47 +8062,47 @@
         <v>15</v>
       </c>
       <c r="B59" s="10">
-        <f>'By Round'!A51</f>
+        <f>'By Round'!A39</f>
         <v/>
       </c>
       <c r="C59" s="10">
-        <f>'By Round'!B51</f>
+        <f>'By Round'!B39</f>
         <v/>
       </c>
       <c r="D59" s="10">
-        <f>'By Round'!C51</f>
+        <f>'By Round'!C39</f>
         <v/>
       </c>
       <c r="E59" s="10">
-        <f>'By Round'!D51</f>
+        <f>'By Round'!D39</f>
         <v/>
       </c>
       <c r="F59" s="10">
-        <f>IF(ISBLANK('By Round'!F53),"",'By Round'!F53)</f>
+        <f>IF(ISBLANK('By Round'!F41),"",'By Round'!F41)</f>
         <v/>
       </c>
       <c r="G59">
-        <f>IF(ISBLANK('By Round'!G53),"",'By Round'!G53)</f>
+        <f>IF(ISBLANK('By Round'!G41),"",'By Round'!G41)</f>
         <v/>
       </c>
       <c r="H59">
-        <f>IF(ISBLANK('By Round'!H53),"",'By Round'!H53)</f>
+        <f>IF(ISBLANK('By Round'!H41),"",'By Round'!H41)</f>
         <v/>
       </c>
       <c r="I59">
-        <f>IF(ISBLANK('By Round'!I53),"",'By Round'!I53)</f>
+        <f>IF(ISBLANK('By Round'!I41),"",'By Round'!I41)</f>
         <v/>
       </c>
       <c r="J59">
-        <f>IF(ISBLANK('By Round'!J53),"",'By Round'!J53)</f>
+        <f>IF(ISBLANK('By Round'!J41),"",'By Round'!J41)</f>
         <v/>
       </c>
       <c r="K59">
-        <f>IF(ISBLANK('By Round'!K53),"",'By Round'!K53)</f>
+        <f>IF(ISBLANK('By Round'!K41),"",'By Round'!K41)</f>
         <v/>
       </c>
       <c r="L59">
-        <f>IF(ISBLANK('By Round'!L53),"",'By Round'!L53)</f>
+        <f>IF(ISBLANK('By Round'!L41),"",'By Round'!L41)</f>
         <v/>
       </c>
       <c r="M59" s="11">
@@ -8188,47 +8188,47 @@
     </row>
     <row r="60">
       <c r="B60" s="10">
-        <f>'By Round'!A39</f>
+        <f>'By Round'!A30</f>
         <v/>
       </c>
       <c r="C60" s="10">
-        <f>'By Round'!B42</f>
+        <f>'By Round'!B33</f>
         <v/>
       </c>
       <c r="D60" s="10">
-        <f>'By Round'!C42</f>
+        <f>'By Round'!C33</f>
         <v/>
       </c>
       <c r="E60" s="10">
-        <f>'By Round'!D42</f>
+        <f>'By Round'!D33</f>
         <v/>
       </c>
       <c r="F60" s="10">
-        <f>IF(ISBLANK('By Round'!F44),"",'By Round'!F44)</f>
+        <f>IF(ISBLANK('By Round'!F35),"",'By Round'!F35)</f>
         <v/>
       </c>
       <c r="G60">
-        <f>IF(ISBLANK('By Round'!G44),"",'By Round'!G44)</f>
+        <f>IF(ISBLANK('By Round'!G35),"",'By Round'!G35)</f>
         <v/>
       </c>
       <c r="H60">
-        <f>IF(ISBLANK('By Round'!H44),"",'By Round'!H44)</f>
+        <f>IF(ISBLANK('By Round'!H35),"",'By Round'!H35)</f>
         <v/>
       </c>
       <c r="I60">
-        <f>IF(ISBLANK('By Round'!I44),"",'By Round'!I44)</f>
+        <f>IF(ISBLANK('By Round'!I35),"",'By Round'!I35)</f>
         <v/>
       </c>
       <c r="J60">
-        <f>IF(ISBLANK('By Round'!J44),"",'By Round'!J44)</f>
+        <f>IF(ISBLANK('By Round'!J35),"",'By Round'!J35)</f>
         <v/>
       </c>
       <c r="K60">
-        <f>IF(ISBLANK('By Round'!K44),"",'By Round'!K44)</f>
+        <f>IF(ISBLANK('By Round'!K35),"",'By Round'!K35)</f>
         <v/>
       </c>
       <c r="L60">
-        <f>IF(ISBLANK('By Round'!L44),"",'By Round'!L44)</f>
+        <f>IF(ISBLANK('By Round'!L35),"",'By Round'!L35)</f>
         <v/>
       </c>
       <c r="M60" s="11">
@@ -8314,47 +8314,47 @@
     </row>
     <row r="61">
       <c r="B61" s="10">
-        <f>'By Round'!A27</f>
+        <f>'By Round'!A21</f>
         <v/>
       </c>
       <c r="C61" s="10">
-        <f>'By Round'!B33</f>
+        <f>'By Round'!B27</f>
         <v/>
       </c>
       <c r="D61" s="10">
-        <f>'By Round'!C33</f>
+        <f>'By Round'!C27</f>
         <v/>
       </c>
       <c r="E61" s="10">
-        <f>'By Round'!D33</f>
+        <f>'By Round'!D27</f>
         <v/>
       </c>
       <c r="F61" s="10">
-        <f>IF(ISBLANK('By Round'!F35),"",'By Round'!F35)</f>
+        <f>IF(ISBLANK('By Round'!F29),"",'By Round'!F29)</f>
         <v/>
       </c>
       <c r="G61">
-        <f>IF(ISBLANK('By Round'!G35),"",'By Round'!G35)</f>
+        <f>IF(ISBLANK('By Round'!G29),"",'By Round'!G29)</f>
         <v/>
       </c>
       <c r="H61">
-        <f>IF(ISBLANK('By Round'!H35),"",'By Round'!H35)</f>
+        <f>IF(ISBLANK('By Round'!H29),"",'By Round'!H29)</f>
         <v/>
       </c>
       <c r="I61">
-        <f>IF(ISBLANK('By Round'!I35),"",'By Round'!I35)</f>
+        <f>IF(ISBLANK('By Round'!I29),"",'By Round'!I29)</f>
         <v/>
       </c>
       <c r="J61">
-        <f>IF(ISBLANK('By Round'!J35),"",'By Round'!J35)</f>
+        <f>IF(ISBLANK('By Round'!J29),"",'By Round'!J29)</f>
         <v/>
       </c>
       <c r="K61">
-        <f>IF(ISBLANK('By Round'!K35),"",'By Round'!K35)</f>
+        <f>IF(ISBLANK('By Round'!K29),"",'By Round'!K29)</f>
         <v/>
       </c>
       <c r="L61">
-        <f>IF(ISBLANK('By Round'!L35),"",'By Round'!L35)</f>
+        <f>IF(ISBLANK('By Round'!L29),"",'By Round'!L29)</f>
         <v/>
       </c>
       <c r="M61" s="11">
@@ -8570,47 +8570,47 @@
         <v>16</v>
       </c>
       <c r="B63" s="10">
-        <f>'By Round'!A63</f>
+        <f>'By Round'!A48</f>
         <v/>
       </c>
       <c r="C63" s="10">
-        <f>'By Round'!B63</f>
+        <f>'By Round'!B48</f>
         <v/>
       </c>
       <c r="D63" s="10">
-        <f>'By Round'!C63</f>
+        <f>'By Round'!C48</f>
         <v/>
       </c>
       <c r="E63" s="10">
-        <f>'By Round'!D63</f>
+        <f>'By Round'!D48</f>
         <v/>
       </c>
       <c r="F63" s="10">
-        <f>IF(ISBLANK('By Round'!F63),"",'By Round'!F63)</f>
+        <f>IF(ISBLANK('By Round'!F48),"",'By Round'!F48)</f>
         <v/>
       </c>
       <c r="G63">
-        <f>IF(ISBLANK('By Round'!G63),"",'By Round'!G63)</f>
+        <f>IF(ISBLANK('By Round'!G48),"",'By Round'!G48)</f>
         <v/>
       </c>
       <c r="H63">
-        <f>IF(ISBLANK('By Round'!H63),"",'By Round'!H63)</f>
+        <f>IF(ISBLANK('By Round'!H48),"",'By Round'!H48)</f>
         <v/>
       </c>
       <c r="I63">
-        <f>IF(ISBLANK('By Round'!I63),"",'By Round'!I63)</f>
+        <f>IF(ISBLANK('By Round'!I48),"",'By Round'!I48)</f>
         <v/>
       </c>
       <c r="J63">
-        <f>IF(ISBLANK('By Round'!J63),"",'By Round'!J63)</f>
+        <f>IF(ISBLANK('By Round'!J48),"",'By Round'!J48)</f>
         <v/>
       </c>
       <c r="K63">
-        <f>IF(ISBLANK('By Round'!K63),"",'By Round'!K63)</f>
+        <f>IF(ISBLANK('By Round'!K48),"",'By Round'!K48)</f>
         <v/>
       </c>
       <c r="L63">
-        <f>IF(ISBLANK('By Round'!L63),"",'By Round'!L63)</f>
+        <f>IF(ISBLANK('By Round'!L48),"",'By Round'!L48)</f>
         <v/>
       </c>
       <c r="M63" s="11">
@@ -8696,47 +8696,47 @@
     </row>
     <row r="64">
       <c r="B64" s="10">
-        <f>'By Round'!A15</f>
+        <f>'By Round'!A12</f>
         <v/>
       </c>
       <c r="C64" s="10">
-        <f>'By Round'!B24</f>
+        <f>'By Round'!B21</f>
         <v/>
       </c>
       <c r="D64" s="10">
-        <f>'By Round'!C24</f>
+        <f>'By Round'!C21</f>
         <v/>
       </c>
       <c r="E64" s="10">
-        <f>'By Round'!D24</f>
+        <f>'By Round'!D21</f>
         <v/>
       </c>
       <c r="F64" s="10">
-        <f>IF(ISBLANK('By Round'!F24),"",'By Round'!F24)</f>
+        <f>IF(ISBLANK('By Round'!F21),"",'By Round'!F21)</f>
         <v/>
       </c>
       <c r="G64">
-        <f>IF(ISBLANK('By Round'!G24),"",'By Round'!G24)</f>
+        <f>IF(ISBLANK('By Round'!G21),"",'By Round'!G21)</f>
         <v/>
       </c>
       <c r="H64">
-        <f>IF(ISBLANK('By Round'!H24),"",'By Round'!H24)</f>
+        <f>IF(ISBLANK('By Round'!H21),"",'By Round'!H21)</f>
         <v/>
       </c>
       <c r="I64">
-        <f>IF(ISBLANK('By Round'!I24),"",'By Round'!I24)</f>
+        <f>IF(ISBLANK('By Round'!I21),"",'By Round'!I21)</f>
         <v/>
       </c>
       <c r="J64">
-        <f>IF(ISBLANK('By Round'!J24),"",'By Round'!J24)</f>
+        <f>IF(ISBLANK('By Round'!J21),"",'By Round'!J21)</f>
         <v/>
       </c>
       <c r="K64">
-        <f>IF(ISBLANK('By Round'!K24),"",'By Round'!K24)</f>
+        <f>IF(ISBLANK('By Round'!K21),"",'By Round'!K21)</f>
         <v/>
       </c>
       <c r="L64">
-        <f>IF(ISBLANK('By Round'!L24),"",'By Round'!L24)</f>
+        <f>IF(ISBLANK('By Round'!L21),"",'By Round'!L21)</f>
         <v/>
       </c>
       <c r="M64" s="11">
@@ -8822,47 +8822,47 @@
     </row>
     <row r="65">
       <c r="B65" s="10">
-        <f>'By Round'!A51</f>
+        <f>'By Round'!A39</f>
         <v/>
       </c>
       <c r="C65" s="10">
-        <f>'By Round'!B54</f>
+        <f>'By Round'!B42</f>
         <v/>
       </c>
       <c r="D65" s="10">
-        <f>'By Round'!C54</f>
+        <f>'By Round'!C42</f>
         <v/>
       </c>
       <c r="E65" s="10">
-        <f>'By Round'!D54</f>
+        <f>'By Round'!D42</f>
         <v/>
       </c>
       <c r="F65" s="10">
-        <f>IF(ISBLANK('By Round'!F54),"",'By Round'!F54)</f>
+        <f>IF(ISBLANK('By Round'!F42),"",'By Round'!F42)</f>
         <v/>
       </c>
       <c r="G65">
-        <f>IF(ISBLANK('By Round'!G54),"",'By Round'!G54)</f>
+        <f>IF(ISBLANK('By Round'!G42),"",'By Round'!G42)</f>
         <v/>
       </c>
       <c r="H65">
-        <f>IF(ISBLANK('By Round'!H54),"",'By Round'!H54)</f>
+        <f>IF(ISBLANK('By Round'!H42),"",'By Round'!H42)</f>
         <v/>
       </c>
       <c r="I65">
-        <f>IF(ISBLANK('By Round'!I54),"",'By Round'!I54)</f>
+        <f>IF(ISBLANK('By Round'!I42),"",'By Round'!I42)</f>
         <v/>
       </c>
       <c r="J65">
-        <f>IF(ISBLANK('By Round'!J54),"",'By Round'!J54)</f>
+        <f>IF(ISBLANK('By Round'!J42),"",'By Round'!J42)</f>
         <v/>
       </c>
       <c r="K65">
-        <f>IF(ISBLANK('By Round'!K54),"",'By Round'!K54)</f>
+        <f>IF(ISBLANK('By Round'!K42),"",'By Round'!K42)</f>
         <v/>
       </c>
       <c r="L65">
-        <f>IF(ISBLANK('By Round'!L54),"",'By Round'!L54)</f>
+        <f>IF(ISBLANK('By Round'!L42),"",'By Round'!L42)</f>
         <v/>
       </c>
       <c r="M65" s="11">
@@ -8949,47 +8949,47 @@
     <row r="66">
       <c r="A66" s="15" t="n"/>
       <c r="B66" s="16">
-        <f>'By Round'!A39</f>
+        <f>'By Round'!A30</f>
         <v/>
       </c>
       <c r="C66" s="16">
-        <f>'By Round'!B45</f>
+        <f>'By Round'!B36</f>
         <v/>
       </c>
       <c r="D66" s="16">
-        <f>'By Round'!C45</f>
+        <f>'By Round'!C36</f>
         <v/>
       </c>
       <c r="E66" s="16">
-        <f>'By Round'!D45</f>
+        <f>'By Round'!D36</f>
         <v/>
       </c>
       <c r="F66" s="16">
-        <f>IF(ISBLANK('By Round'!F45),"",'By Round'!F45)</f>
+        <f>IF(ISBLANK('By Round'!F36),"",'By Round'!F36)</f>
         <v/>
       </c>
       <c r="G66" s="15">
-        <f>IF(ISBLANK('By Round'!G45),"",'By Round'!G45)</f>
+        <f>IF(ISBLANK('By Round'!G36),"",'By Round'!G36)</f>
         <v/>
       </c>
       <c r="H66" s="15">
-        <f>IF(ISBLANK('By Round'!H45),"",'By Round'!H45)</f>
+        <f>IF(ISBLANK('By Round'!H36),"",'By Round'!H36)</f>
         <v/>
       </c>
       <c r="I66" s="15">
-        <f>IF(ISBLANK('By Round'!I45),"",'By Round'!I45)</f>
+        <f>IF(ISBLANK('By Round'!I36),"",'By Round'!I36)</f>
         <v/>
       </c>
       <c r="J66" s="15">
-        <f>IF(ISBLANK('By Round'!J45),"",'By Round'!J45)</f>
+        <f>IF(ISBLANK('By Round'!J36),"",'By Round'!J36)</f>
         <v/>
       </c>
       <c r="K66" s="15">
-        <f>IF(ISBLANK('By Round'!K45),"",'By Round'!K45)</f>
+        <f>IF(ISBLANK('By Round'!K36),"",'By Round'!K36)</f>
         <v/>
       </c>
       <c r="L66" s="15">
-        <f>IF(ISBLANK('By Round'!L45),"",'By Round'!L45)</f>
+        <f>IF(ISBLANK('By Round'!L36),"",'By Round'!L36)</f>
         <v/>
       </c>
       <c r="M66" s="17">
@@ -9078,47 +9078,47 @@
         <v>17</v>
       </c>
       <c r="B67" s="10">
-        <f>'By Round'!A63</f>
+        <f>'By Round'!A48</f>
         <v/>
       </c>
       <c r="C67" s="10">
-        <f>'By Round'!B63</f>
+        <f>'By Round'!B48</f>
         <v/>
       </c>
       <c r="D67" s="10">
-        <f>'By Round'!C63</f>
+        <f>'By Round'!C48</f>
         <v/>
       </c>
       <c r="E67" s="10">
-        <f>'By Round'!D63</f>
+        <f>'By Round'!D48</f>
         <v/>
       </c>
       <c r="F67" s="10">
-        <f>IF(ISBLANK('By Round'!F64),"",'By Round'!F64)</f>
+        <f>IF(ISBLANK('By Round'!F49),"",'By Round'!F49)</f>
         <v/>
       </c>
       <c r="G67">
-        <f>IF(ISBLANK('By Round'!G64),"",'By Round'!G64)</f>
+        <f>IF(ISBLANK('By Round'!G49),"",'By Round'!G49)</f>
         <v/>
       </c>
       <c r="H67">
-        <f>IF(ISBLANK('By Round'!H64),"",'By Round'!H64)</f>
+        <f>IF(ISBLANK('By Round'!H49),"",'By Round'!H49)</f>
         <v/>
       </c>
       <c r="I67">
-        <f>IF(ISBLANK('By Round'!I64),"",'By Round'!I64)</f>
+        <f>IF(ISBLANK('By Round'!I49),"",'By Round'!I49)</f>
         <v/>
       </c>
       <c r="J67">
-        <f>IF(ISBLANK('By Round'!J64),"",'By Round'!J64)</f>
+        <f>IF(ISBLANK('By Round'!J49),"",'By Round'!J49)</f>
         <v/>
       </c>
       <c r="K67">
-        <f>IF(ISBLANK('By Round'!K64),"",'By Round'!K64)</f>
+        <f>IF(ISBLANK('By Round'!K49),"",'By Round'!K49)</f>
         <v/>
       </c>
       <c r="L67">
-        <f>IF(ISBLANK('By Round'!L64),"",'By Round'!L64)</f>
+        <f>IF(ISBLANK('By Round'!L49),"",'By Round'!L49)</f>
         <v/>
       </c>
       <c r="M67" s="11">
@@ -9204,47 +9204,47 @@
     </row>
     <row r="68">
       <c r="B68" s="10">
-        <f>'By Round'!A15</f>
+        <f>'By Round'!A12</f>
         <v/>
       </c>
       <c r="C68" s="10">
-        <f>'By Round'!B24</f>
+        <f>'By Round'!B21</f>
         <v/>
       </c>
       <c r="D68" s="10">
-        <f>'By Round'!C24</f>
+        <f>'By Round'!C21</f>
         <v/>
       </c>
       <c r="E68" s="10">
-        <f>'By Round'!D24</f>
+        <f>'By Round'!D21</f>
         <v/>
       </c>
       <c r="F68" s="10">
-        <f>IF(ISBLANK('By Round'!F25),"",'By Round'!F25)</f>
+        <f>IF(ISBLANK('By Round'!F22),"",'By Round'!F22)</f>
         <v/>
       </c>
       <c r="G68">
-        <f>IF(ISBLANK('By Round'!G25),"",'By Round'!G25)</f>
+        <f>IF(ISBLANK('By Round'!G22),"",'By Round'!G22)</f>
         <v/>
       </c>
       <c r="H68">
-        <f>IF(ISBLANK('By Round'!H25),"",'By Round'!H25)</f>
+        <f>IF(ISBLANK('By Round'!H22),"",'By Round'!H22)</f>
         <v/>
       </c>
       <c r="I68">
-        <f>IF(ISBLANK('By Round'!I25),"",'By Round'!I25)</f>
+        <f>IF(ISBLANK('By Round'!I22),"",'By Round'!I22)</f>
         <v/>
       </c>
       <c r="J68">
-        <f>IF(ISBLANK('By Round'!J25),"",'By Round'!J25)</f>
+        <f>IF(ISBLANK('By Round'!J22),"",'By Round'!J22)</f>
         <v/>
       </c>
       <c r="K68">
-        <f>IF(ISBLANK('By Round'!K25),"",'By Round'!K25)</f>
+        <f>IF(ISBLANK('By Round'!K22),"",'By Round'!K22)</f>
         <v/>
       </c>
       <c r="L68">
-        <f>IF(ISBLANK('By Round'!L25),"",'By Round'!L25)</f>
+        <f>IF(ISBLANK('By Round'!L22),"",'By Round'!L22)</f>
         <v/>
       </c>
       <c r="M68" s="11">
@@ -9330,47 +9330,47 @@
     </row>
     <row r="69">
       <c r="B69" s="10">
-        <f>'By Round'!A51</f>
+        <f>'By Round'!A39</f>
         <v/>
       </c>
       <c r="C69" s="10">
-        <f>'By Round'!B54</f>
+        <f>'By Round'!B42</f>
         <v/>
       </c>
       <c r="D69" s="10">
-        <f>'By Round'!C54</f>
+        <f>'By Round'!C42</f>
         <v/>
       </c>
       <c r="E69" s="10">
-        <f>'By Round'!D54</f>
+        <f>'By Round'!D42</f>
         <v/>
       </c>
       <c r="F69" s="10">
-        <f>IF(ISBLANK('By Round'!F55),"",'By Round'!F55)</f>
+        <f>IF(ISBLANK('By Round'!F43),"",'By Round'!F43)</f>
         <v/>
       </c>
       <c r="G69">
-        <f>IF(ISBLANK('By Round'!G55),"",'By Round'!G55)</f>
+        <f>IF(ISBLANK('By Round'!G43),"",'By Round'!G43)</f>
         <v/>
       </c>
       <c r="H69">
-        <f>IF(ISBLANK('By Round'!H55),"",'By Round'!H55)</f>
+        <f>IF(ISBLANK('By Round'!H43),"",'By Round'!H43)</f>
         <v/>
       </c>
       <c r="I69">
-        <f>IF(ISBLANK('By Round'!I55),"",'By Round'!I55)</f>
+        <f>IF(ISBLANK('By Round'!I43),"",'By Round'!I43)</f>
         <v/>
       </c>
       <c r="J69">
-        <f>IF(ISBLANK('By Round'!J55),"",'By Round'!J55)</f>
+        <f>IF(ISBLANK('By Round'!J43),"",'By Round'!J43)</f>
         <v/>
       </c>
       <c r="K69">
-        <f>IF(ISBLANK('By Round'!K55),"",'By Round'!K55)</f>
+        <f>IF(ISBLANK('By Round'!K43),"",'By Round'!K43)</f>
         <v/>
       </c>
       <c r="L69">
-        <f>IF(ISBLANK('By Round'!L55),"",'By Round'!L55)</f>
+        <f>IF(ISBLANK('By Round'!L43),"",'By Round'!L43)</f>
         <v/>
       </c>
       <c r="M69" s="11">
@@ -9457,47 +9457,47 @@
     <row r="70">
       <c r="A70" s="15" t="n"/>
       <c r="B70" s="16">
-        <f>'By Round'!A39</f>
+        <f>'By Round'!A30</f>
         <v/>
       </c>
       <c r="C70" s="16">
-        <f>'By Round'!B45</f>
+        <f>'By Round'!B36</f>
         <v/>
       </c>
       <c r="D70" s="16">
-        <f>'By Round'!C45</f>
+        <f>'By Round'!C36</f>
         <v/>
       </c>
       <c r="E70" s="16">
-        <f>'By Round'!D45</f>
+        <f>'By Round'!D36</f>
         <v/>
       </c>
       <c r="F70" s="16">
-        <f>IF(ISBLANK('By Round'!F46),"",'By Round'!F46)</f>
+        <f>IF(ISBLANK('By Round'!F37),"",'By Round'!F37)</f>
         <v/>
       </c>
       <c r="G70" s="15">
-        <f>IF(ISBLANK('By Round'!G46),"",'By Round'!G46)</f>
+        <f>IF(ISBLANK('By Round'!G37),"",'By Round'!G37)</f>
         <v/>
       </c>
       <c r="H70" s="15">
-        <f>IF(ISBLANK('By Round'!H46),"",'By Round'!H46)</f>
+        <f>IF(ISBLANK('By Round'!H37),"",'By Round'!H37)</f>
         <v/>
       </c>
       <c r="I70" s="15">
-        <f>IF(ISBLANK('By Round'!I46),"",'By Round'!I46)</f>
+        <f>IF(ISBLANK('By Round'!I37),"",'By Round'!I37)</f>
         <v/>
       </c>
       <c r="J70" s="15">
-        <f>IF(ISBLANK('By Round'!J46),"",'By Round'!J46)</f>
+        <f>IF(ISBLANK('By Round'!J37),"",'By Round'!J37)</f>
         <v/>
       </c>
       <c r="K70" s="15">
-        <f>IF(ISBLANK('By Round'!K46),"",'By Round'!K46)</f>
+        <f>IF(ISBLANK('By Round'!K37),"",'By Round'!K37)</f>
         <v/>
       </c>
       <c r="L70" s="15">
-        <f>IF(ISBLANK('By Round'!L46),"",'By Round'!L46)</f>
+        <f>IF(ISBLANK('By Round'!L37),"",'By Round'!L37)</f>
         <v/>
       </c>
       <c r="M70" s="17">
@@ -9586,47 +9586,47 @@
         <v>18</v>
       </c>
       <c r="B71" s="10">
-        <f>'By Round'!A63</f>
+        <f>'By Round'!A48</f>
         <v/>
       </c>
       <c r="C71" s="10">
-        <f>'By Round'!B63</f>
+        <f>'By Round'!B48</f>
         <v/>
       </c>
       <c r="D71" s="10">
-        <f>'By Round'!C63</f>
+        <f>'By Round'!C48</f>
         <v/>
       </c>
       <c r="E71" s="10">
-        <f>'By Round'!D63</f>
+        <f>'By Round'!D48</f>
         <v/>
       </c>
       <c r="F71" s="10">
-        <f>IF(ISBLANK('By Round'!F65),"",'By Round'!F65)</f>
+        <f>IF(ISBLANK('By Round'!F50),"",'By Round'!F50)</f>
         <v/>
       </c>
       <c r="G71">
-        <f>IF(ISBLANK('By Round'!G65),"",'By Round'!G65)</f>
+        <f>IF(ISBLANK('By Round'!G50),"",'By Round'!G50)</f>
         <v/>
       </c>
       <c r="H71">
-        <f>IF(ISBLANK('By Round'!H65),"",'By Round'!H65)</f>
+        <f>IF(ISBLANK('By Round'!H50),"",'By Round'!H50)</f>
         <v/>
       </c>
       <c r="I71">
-        <f>IF(ISBLANK('By Round'!I65),"",'By Round'!I65)</f>
+        <f>IF(ISBLANK('By Round'!I50),"",'By Round'!I50)</f>
         <v/>
       </c>
       <c r="J71">
-        <f>IF(ISBLANK('By Round'!J65),"",'By Round'!J65)</f>
+        <f>IF(ISBLANK('By Round'!J50),"",'By Round'!J50)</f>
         <v/>
       </c>
       <c r="K71">
-        <f>IF(ISBLANK('By Round'!K65),"",'By Round'!K65)</f>
+        <f>IF(ISBLANK('By Round'!K50),"",'By Round'!K50)</f>
         <v/>
       </c>
       <c r="L71">
-        <f>IF(ISBLANK('By Round'!L65),"",'By Round'!L65)</f>
+        <f>IF(ISBLANK('By Round'!L50),"",'By Round'!L50)</f>
         <v/>
       </c>
       <c r="M71" s="11">
@@ -9712,47 +9712,47 @@
     </row>
     <row r="72">
       <c r="B72" s="10">
-        <f>'By Round'!A15</f>
+        <f>'By Round'!A12</f>
         <v/>
       </c>
       <c r="C72" s="10">
-        <f>'By Round'!B24</f>
+        <f>'By Round'!B21</f>
         <v/>
       </c>
       <c r="D72" s="10">
-        <f>'By Round'!C24</f>
+        <f>'By Round'!C21</f>
         <v/>
       </c>
       <c r="E72" s="10">
-        <f>'By Round'!D24</f>
+        <f>'By Round'!D21</f>
         <v/>
       </c>
       <c r="F72" s="10">
-        <f>IF(ISBLANK('By Round'!F26),"",'By Round'!F26)</f>
+        <f>IF(ISBLANK('By Round'!F23),"",'By Round'!F23)</f>
         <v/>
       </c>
       <c r="G72">
-        <f>IF(ISBLANK('By Round'!G26),"",'By Round'!G26)</f>
+        <f>IF(ISBLANK('By Round'!G23),"",'By Round'!G23)</f>
         <v/>
       </c>
       <c r="H72">
-        <f>IF(ISBLANK('By Round'!H26),"",'By Round'!H26)</f>
+        <f>IF(ISBLANK('By Round'!H23),"",'By Round'!H23)</f>
         <v/>
       </c>
       <c r="I72">
-        <f>IF(ISBLANK('By Round'!I26),"",'By Round'!I26)</f>
+        <f>IF(ISBLANK('By Round'!I23),"",'By Round'!I23)</f>
         <v/>
       </c>
       <c r="J72">
-        <f>IF(ISBLANK('By Round'!J26),"",'By Round'!J26)</f>
+        <f>IF(ISBLANK('By Round'!J23),"",'By Round'!J23)</f>
         <v/>
       </c>
       <c r="K72">
-        <f>IF(ISBLANK('By Round'!K26),"",'By Round'!K26)</f>
+        <f>IF(ISBLANK('By Round'!K23),"",'By Round'!K23)</f>
         <v/>
       </c>
       <c r="L72">
-        <f>IF(ISBLANK('By Round'!L26),"",'By Round'!L26)</f>
+        <f>IF(ISBLANK('By Round'!L23),"",'By Round'!L23)</f>
         <v/>
       </c>
       <c r="M72" s="11">
@@ -9838,47 +9838,47 @@
     </row>
     <row r="73">
       <c r="B73" s="10">
-        <f>'By Round'!A51</f>
+        <f>'By Round'!A39</f>
         <v/>
       </c>
       <c r="C73" s="10">
-        <f>'By Round'!B54</f>
+        <f>'By Round'!B42</f>
         <v/>
       </c>
       <c r="D73" s="10">
-        <f>'By Round'!C54</f>
+        <f>'By Round'!C42</f>
         <v/>
       </c>
       <c r="E73" s="10">
-        <f>'By Round'!D54</f>
+        <f>'By Round'!D42</f>
         <v/>
       </c>
       <c r="F73" s="10">
-        <f>IF(ISBLANK('By Round'!F56),"",'By Round'!F56)</f>
+        <f>IF(ISBLANK('By Round'!F44),"",'By Round'!F44)</f>
         <v/>
       </c>
       <c r="G73">
-        <f>IF(ISBLANK('By Round'!G56),"",'By Round'!G56)</f>
+        <f>IF(ISBLANK('By Round'!G44),"",'By Round'!G44)</f>
         <v/>
       </c>
       <c r="H73">
-        <f>IF(ISBLANK('By Round'!H56),"",'By Round'!H56)</f>
+        <f>IF(ISBLANK('By Round'!H44),"",'By Round'!H44)</f>
         <v/>
       </c>
       <c r="I73">
-        <f>IF(ISBLANK('By Round'!I56),"",'By Round'!I56)</f>
+        <f>IF(ISBLANK('By Round'!I44),"",'By Round'!I44)</f>
         <v/>
       </c>
       <c r="J73">
-        <f>IF(ISBLANK('By Round'!J56),"",'By Round'!J56)</f>
+        <f>IF(ISBLANK('By Round'!J44),"",'By Round'!J44)</f>
         <v/>
       </c>
       <c r="K73">
-        <f>IF(ISBLANK('By Round'!K56),"",'By Round'!K56)</f>
+        <f>IF(ISBLANK('By Round'!K44),"",'By Round'!K44)</f>
         <v/>
       </c>
       <c r="L73">
-        <f>IF(ISBLANK('By Round'!L56),"",'By Round'!L56)</f>
+        <f>IF(ISBLANK('By Round'!L44),"",'By Round'!L44)</f>
         <v/>
       </c>
       <c r="M73" s="11">
@@ -9965,47 +9965,47 @@
     <row r="74">
       <c r="A74" s="15" t="n"/>
       <c r="B74" s="16">
-        <f>'By Round'!A39</f>
+        <f>'By Round'!A30</f>
         <v/>
       </c>
       <c r="C74" s="16">
-        <f>'By Round'!B45</f>
+        <f>'By Round'!B36</f>
         <v/>
       </c>
       <c r="D74" s="16">
-        <f>'By Round'!C45</f>
+        <f>'By Round'!C36</f>
         <v/>
       </c>
       <c r="E74" s="16">
-        <f>'By Round'!D45</f>
+        <f>'By Round'!D36</f>
         <v/>
       </c>
       <c r="F74" s="16">
-        <f>IF(ISBLANK('By Round'!F47),"",'By Round'!F47)</f>
+        <f>IF(ISBLANK('By Round'!F38),"",'By Round'!F38)</f>
         <v/>
       </c>
       <c r="G74" s="15">
-        <f>IF(ISBLANK('By Round'!G47),"",'By Round'!G47)</f>
+        <f>IF(ISBLANK('By Round'!G38),"",'By Round'!G38)</f>
         <v/>
       </c>
       <c r="H74" s="15">
-        <f>IF(ISBLANK('By Round'!H47),"",'By Round'!H47)</f>
+        <f>IF(ISBLANK('By Round'!H38),"",'By Round'!H38)</f>
         <v/>
       </c>
       <c r="I74" s="15">
-        <f>IF(ISBLANK('By Round'!I47),"",'By Round'!I47)</f>
+        <f>IF(ISBLANK('By Round'!I38),"",'By Round'!I38)</f>
         <v/>
       </c>
       <c r="J74" s="15">
-        <f>IF(ISBLANK('By Round'!J47),"",'By Round'!J47)</f>
+        <f>IF(ISBLANK('By Round'!J38),"",'By Round'!J38)</f>
         <v/>
       </c>
       <c r="K74" s="15">
-        <f>IF(ISBLANK('By Round'!K47),"",'By Round'!K47)</f>
+        <f>IF(ISBLANK('By Round'!K38),"",'By Round'!K38)</f>
         <v/>
       </c>
       <c r="L74" s="15">
-        <f>IF(ISBLANK('By Round'!L47),"",'By Round'!L47)</f>
+        <f>IF(ISBLANK('By Round'!L38),"",'By Round'!L38)</f>
         <v/>
       </c>
       <c r="M74" s="17">
@@ -10094,47 +10094,47 @@
         <v>19</v>
       </c>
       <c r="B75" s="10">
-        <f>'By Round'!A75</f>
+        <f>'By Round'!A57</f>
         <v/>
       </c>
       <c r="C75" s="10">
-        <f>'By Round'!B75</f>
+        <f>'By Round'!B57</f>
         <v/>
       </c>
       <c r="D75" s="10">
-        <f>'By Round'!C75</f>
+        <f>'By Round'!C57</f>
         <v/>
       </c>
       <c r="E75" s="10">
-        <f>'By Round'!D75</f>
+        <f>'By Round'!D57</f>
         <v/>
       </c>
       <c r="F75" s="10">
-        <f>IF(ISBLANK('By Round'!F75),"",'By Round'!F75)</f>
+        <f>IF(ISBLANK('By Round'!F57),"",'By Round'!F57)</f>
         <v/>
       </c>
       <c r="G75">
-        <f>IF(ISBLANK('By Round'!G75),"",'By Round'!G75)</f>
+        <f>IF(ISBLANK('By Round'!G57),"",'By Round'!G57)</f>
         <v/>
       </c>
       <c r="H75">
-        <f>IF(ISBLANK('By Round'!H75),"",'By Round'!H75)</f>
+        <f>IF(ISBLANK('By Round'!H57),"",'By Round'!H57)</f>
         <v/>
       </c>
       <c r="I75">
-        <f>IF(ISBLANK('By Round'!I75),"",'By Round'!I75)</f>
+        <f>IF(ISBLANK('By Round'!I57),"",'By Round'!I57)</f>
         <v/>
       </c>
       <c r="J75">
-        <f>IF(ISBLANK('By Round'!J75),"",'By Round'!J75)</f>
+        <f>IF(ISBLANK('By Round'!J57),"",'By Round'!J57)</f>
         <v/>
       </c>
       <c r="K75">
-        <f>IF(ISBLANK('By Round'!K75),"",'By Round'!K75)</f>
+        <f>IF(ISBLANK('By Round'!K57),"",'By Round'!K57)</f>
         <v/>
       </c>
       <c r="L75">
-        <f>IF(ISBLANK('By Round'!L75),"",'By Round'!L75)</f>
+        <f>IF(ISBLANK('By Round'!L57),"",'By Round'!L57)</f>
         <v/>
       </c>
       <c r="M75" s="11">
@@ -10220,47 +10220,47 @@
     </row>
     <row r="76">
       <c r="B76" s="10">
-        <f>'By Round'!A51</f>
+        <f>'By Round'!A39</f>
         <v/>
       </c>
       <c r="C76" s="10">
-        <f>'By Round'!B57</f>
+        <f>'By Round'!B45</f>
         <v/>
       </c>
       <c r="D76" s="10">
-        <f>'By Round'!C57</f>
+        <f>'By Round'!C45</f>
         <v/>
       </c>
       <c r="E76" s="10">
-        <f>'By Round'!D57</f>
+        <f>'By Round'!D45</f>
         <v/>
       </c>
       <c r="F76" s="10">
-        <f>IF(ISBLANK('By Round'!F57),"",'By Round'!F57)</f>
+        <f>IF(ISBLANK('By Round'!F45),"",'By Round'!F45)</f>
         <v/>
       </c>
       <c r="G76">
-        <f>IF(ISBLANK('By Round'!G57),"",'By Round'!G57)</f>
+        <f>IF(ISBLANK('By Round'!G45),"",'By Round'!G45)</f>
         <v/>
       </c>
       <c r="H76">
-        <f>IF(ISBLANK('By Round'!H57),"",'By Round'!H57)</f>
+        <f>IF(ISBLANK('By Round'!H45),"",'By Round'!H45)</f>
         <v/>
       </c>
       <c r="I76">
-        <f>IF(ISBLANK('By Round'!I57),"",'By Round'!I57)</f>
+        <f>IF(ISBLANK('By Round'!I45),"",'By Round'!I45)</f>
         <v/>
       </c>
       <c r="J76">
-        <f>IF(ISBLANK('By Round'!J57),"",'By Round'!J57)</f>
+        <f>IF(ISBLANK('By Round'!J45),"",'By Round'!J45)</f>
         <v/>
       </c>
       <c r="K76">
-        <f>IF(ISBLANK('By Round'!K57),"",'By Round'!K57)</f>
+        <f>IF(ISBLANK('By Round'!K45),"",'By Round'!K45)</f>
         <v/>
       </c>
       <c r="L76">
-        <f>IF(ISBLANK('By Round'!L57),"",'By Round'!L57)</f>
+        <f>IF(ISBLANK('By Round'!L45),"",'By Round'!L45)</f>
         <v/>
       </c>
       <c r="M76" s="11">
@@ -10346,47 +10346,47 @@
     </row>
     <row r="77">
       <c r="B77" s="10">
-        <f>'By Round'!A27</f>
+        <f>'By Round'!A21</f>
         <v/>
       </c>
       <c r="C77" s="10">
-        <f>'By Round'!B36</f>
+        <f>'By Round'!B30</f>
         <v/>
       </c>
       <c r="D77" s="10">
-        <f>'By Round'!C36</f>
+        <f>'By Round'!C30</f>
         <v/>
       </c>
       <c r="E77" s="10">
-        <f>'By Round'!D36</f>
+        <f>'By Round'!D30</f>
         <v/>
       </c>
       <c r="F77" s="10">
-        <f>IF(ISBLANK('By Round'!F36),"",'By Round'!F36)</f>
+        <f>IF(ISBLANK('By Round'!F30),"",'By Round'!F30)</f>
         <v/>
       </c>
       <c r="G77">
-        <f>IF(ISBLANK('By Round'!G36),"",'By Round'!G36)</f>
+        <f>IF(ISBLANK('By Round'!G30),"",'By Round'!G30)</f>
         <v/>
       </c>
       <c r="H77">
-        <f>IF(ISBLANK('By Round'!H36),"",'By Round'!H36)</f>
+        <f>IF(ISBLANK('By Round'!H30),"",'By Round'!H30)</f>
         <v/>
       </c>
       <c r="I77">
-        <f>IF(ISBLANK('By Round'!I36),"",'By Round'!I36)</f>
+        <f>IF(ISBLANK('By Round'!I30),"",'By Round'!I30)</f>
         <v/>
       </c>
       <c r="J77">
-        <f>IF(ISBLANK('By Round'!J36),"",'By Round'!J36)</f>
+        <f>IF(ISBLANK('By Round'!J30),"",'By Round'!J30)</f>
         <v/>
       </c>
       <c r="K77">
-        <f>IF(ISBLANK('By Round'!K36),"",'By Round'!K36)</f>
+        <f>IF(ISBLANK('By Round'!K30),"",'By Round'!K30)</f>
         <v/>
       </c>
       <c r="L77">
-        <f>IF(ISBLANK('By Round'!L36),"",'By Round'!L36)</f>
+        <f>IF(ISBLANK('By Round'!L30),"",'By Round'!L30)</f>
         <v/>
       </c>
       <c r="M77" s="11">
@@ -10473,47 +10473,47 @@
     <row r="78">
       <c r="A78" s="15" t="n"/>
       <c r="B78" s="16">
-        <f>'By Round'!A63</f>
+        <f>'By Round'!A48</f>
         <v/>
       </c>
       <c r="C78" s="16">
-        <f>'By Round'!B66</f>
+        <f>'By Round'!B51</f>
         <v/>
       </c>
       <c r="D78" s="16">
-        <f>'By Round'!C66</f>
+        <f>'By Round'!C51</f>
         <v/>
       </c>
       <c r="E78" s="16">
-        <f>'By Round'!D66</f>
+        <f>'By Round'!D51</f>
         <v/>
       </c>
       <c r="F78" s="16">
-        <f>IF(ISBLANK('By Round'!F66),"",'By Round'!F66)</f>
+        <f>IF(ISBLANK('By Round'!F51),"",'By Round'!F51)</f>
         <v/>
       </c>
       <c r="G78" s="15">
-        <f>IF(ISBLANK('By Round'!G66),"",'By Round'!G66)</f>
+        <f>IF(ISBLANK('By Round'!G51),"",'By Round'!G51)</f>
         <v/>
       </c>
       <c r="H78" s="15">
-        <f>IF(ISBLANK('By Round'!H66),"",'By Round'!H66)</f>
+        <f>IF(ISBLANK('By Round'!H51),"",'By Round'!H51)</f>
         <v/>
       </c>
       <c r="I78" s="15">
-        <f>IF(ISBLANK('By Round'!I66),"",'By Round'!I66)</f>
+        <f>IF(ISBLANK('By Round'!I51),"",'By Round'!I51)</f>
         <v/>
       </c>
       <c r="J78" s="15">
-        <f>IF(ISBLANK('By Round'!J66),"",'By Round'!J66)</f>
+        <f>IF(ISBLANK('By Round'!J51),"",'By Round'!J51)</f>
         <v/>
       </c>
       <c r="K78" s="15">
-        <f>IF(ISBLANK('By Round'!K66),"",'By Round'!K66)</f>
+        <f>IF(ISBLANK('By Round'!K51),"",'By Round'!K51)</f>
         <v/>
       </c>
       <c r="L78" s="15">
-        <f>IF(ISBLANK('By Round'!L66),"",'By Round'!L66)</f>
+        <f>IF(ISBLANK('By Round'!L51),"",'By Round'!L51)</f>
         <v/>
       </c>
       <c r="M78" s="17">
@@ -10602,47 +10602,47 @@
         <v>20</v>
       </c>
       <c r="B79" s="10">
-        <f>'By Round'!A75</f>
+        <f>'By Round'!A57</f>
         <v/>
       </c>
       <c r="C79" s="10">
-        <f>'By Round'!B75</f>
+        <f>'By Round'!B57</f>
         <v/>
       </c>
       <c r="D79" s="10">
-        <f>'By Round'!C75</f>
+        <f>'By Round'!C57</f>
         <v/>
       </c>
       <c r="E79" s="10">
-        <f>'By Round'!D75</f>
+        <f>'By Round'!D57</f>
         <v/>
       </c>
       <c r="F79" s="10">
-        <f>IF(ISBLANK('By Round'!F76),"",'By Round'!F76)</f>
+        <f>IF(ISBLANK('By Round'!F58),"",'By Round'!F58)</f>
         <v/>
       </c>
       <c r="G79">
-        <f>IF(ISBLANK('By Round'!G76),"",'By Round'!G76)</f>
+        <f>IF(ISBLANK('By Round'!G58),"",'By Round'!G58)</f>
         <v/>
       </c>
       <c r="H79">
-        <f>IF(ISBLANK('By Round'!H76),"",'By Round'!H76)</f>
+        <f>IF(ISBLANK('By Round'!H58),"",'By Round'!H58)</f>
         <v/>
       </c>
       <c r="I79">
-        <f>IF(ISBLANK('By Round'!I76),"",'By Round'!I76)</f>
+        <f>IF(ISBLANK('By Round'!I58),"",'By Round'!I58)</f>
         <v/>
       </c>
       <c r="J79">
-        <f>IF(ISBLANK('By Round'!J76),"",'By Round'!J76)</f>
+        <f>IF(ISBLANK('By Round'!J58),"",'By Round'!J58)</f>
         <v/>
       </c>
       <c r="K79">
-        <f>IF(ISBLANK('By Round'!K76),"",'By Round'!K76)</f>
+        <f>IF(ISBLANK('By Round'!K58),"",'By Round'!K58)</f>
         <v/>
       </c>
       <c r="L79">
-        <f>IF(ISBLANK('By Round'!L76),"",'By Round'!L76)</f>
+        <f>IF(ISBLANK('By Round'!L58),"",'By Round'!L58)</f>
         <v/>
       </c>
       <c r="M79" s="11">
@@ -10728,47 +10728,47 @@
     </row>
     <row r="80">
       <c r="B80" s="10">
-        <f>'By Round'!A51</f>
+        <f>'By Round'!A39</f>
         <v/>
       </c>
       <c r="C80" s="10">
-        <f>'By Round'!B57</f>
+        <f>'By Round'!B45</f>
         <v/>
       </c>
       <c r="D80" s="10">
-        <f>'By Round'!C57</f>
+        <f>'By Round'!C45</f>
         <v/>
       </c>
       <c r="E80" s="10">
-        <f>'By Round'!D57</f>
+        <f>'By Round'!D45</f>
         <v/>
       </c>
       <c r="F80" s="10">
-        <f>IF(ISBLANK('By Round'!F58),"",'By Round'!F58)</f>
+        <f>IF(ISBLANK('By Round'!F46),"",'By Round'!F46)</f>
         <v/>
       </c>
       <c r="G80">
-        <f>IF(ISBLANK('By Round'!G58),"",'By Round'!G58)</f>
+        <f>IF(ISBLANK('By Round'!G46),"",'By Round'!G46)</f>
         <v/>
       </c>
       <c r="H80">
-        <f>IF(ISBLANK('By Round'!H58),"",'By Round'!H58)</f>
+        <f>IF(ISBLANK('By Round'!H46),"",'By Round'!H46)</f>
         <v/>
       </c>
       <c r="I80">
-        <f>IF(ISBLANK('By Round'!I58),"",'By Round'!I58)</f>
+        <f>IF(ISBLANK('By Round'!I46),"",'By Round'!I46)</f>
         <v/>
       </c>
       <c r="J80">
-        <f>IF(ISBLANK('By Round'!J58),"",'By Round'!J58)</f>
+        <f>IF(ISBLANK('By Round'!J46),"",'By Round'!J46)</f>
         <v/>
       </c>
       <c r="K80">
-        <f>IF(ISBLANK('By Round'!K58),"",'By Round'!K58)</f>
+        <f>IF(ISBLANK('By Round'!K46),"",'By Round'!K46)</f>
         <v/>
       </c>
       <c r="L80">
-        <f>IF(ISBLANK('By Round'!L58),"",'By Round'!L58)</f>
+        <f>IF(ISBLANK('By Round'!L46),"",'By Round'!L46)</f>
         <v/>
       </c>
       <c r="M80" s="11">
@@ -10854,47 +10854,47 @@
     </row>
     <row r="81">
       <c r="B81" s="10">
-        <f>'By Round'!A27</f>
+        <f>'By Round'!A21</f>
         <v/>
       </c>
       <c r="C81" s="10">
-        <f>'By Round'!B36</f>
+        <f>'By Round'!B30</f>
         <v/>
       </c>
       <c r="D81" s="10">
-        <f>'By Round'!C36</f>
+        <f>'By Round'!C30</f>
         <v/>
       </c>
       <c r="E81" s="10">
-        <f>'By Round'!D36</f>
+        <f>'By Round'!D30</f>
         <v/>
       </c>
       <c r="F81" s="10">
-        <f>IF(ISBLANK('By Round'!F37),"",'By Round'!F37)</f>
+        <f>IF(ISBLANK('By Round'!F31),"",'By Round'!F31)</f>
         <v/>
       </c>
       <c r="G81">
-        <f>IF(ISBLANK('By Round'!G37),"",'By Round'!G37)</f>
+        <f>IF(ISBLANK('By Round'!G31),"",'By Round'!G31)</f>
         <v/>
       </c>
       <c r="H81">
-        <f>IF(ISBLANK('By Round'!H37),"",'By Round'!H37)</f>
+        <f>IF(ISBLANK('By Round'!H31),"",'By Round'!H31)</f>
         <v/>
       </c>
       <c r="I81">
-        <f>IF(ISBLANK('By Round'!I37),"",'By Round'!I37)</f>
+        <f>IF(ISBLANK('By Round'!I31),"",'By Round'!I31)</f>
         <v/>
       </c>
       <c r="J81">
-        <f>IF(ISBLANK('By Round'!J37),"",'By Round'!J37)</f>
+        <f>IF(ISBLANK('By Round'!J31),"",'By Round'!J31)</f>
         <v/>
       </c>
       <c r="K81">
-        <f>IF(ISBLANK('By Round'!K37),"",'By Round'!K37)</f>
+        <f>IF(ISBLANK('By Round'!K31),"",'By Round'!K31)</f>
         <v/>
       </c>
       <c r="L81">
-        <f>IF(ISBLANK('By Round'!L37),"",'By Round'!L37)</f>
+        <f>IF(ISBLANK('By Round'!L31),"",'By Round'!L31)</f>
         <v/>
       </c>
       <c r="M81" s="11">
@@ -10981,47 +10981,47 @@
     <row r="82">
       <c r="A82" s="15" t="n"/>
       <c r="B82" s="16">
-        <f>'By Round'!A63</f>
+        <f>'By Round'!A48</f>
         <v/>
       </c>
       <c r="C82" s="16">
-        <f>'By Round'!B66</f>
+        <f>'By Round'!B51</f>
         <v/>
       </c>
       <c r="D82" s="16">
-        <f>'By Round'!C66</f>
+        <f>'By Round'!C51</f>
         <v/>
       </c>
       <c r="E82" s="16">
-        <f>'By Round'!D66</f>
+        <f>'By Round'!D51</f>
         <v/>
       </c>
       <c r="F82" s="16">
-        <f>IF(ISBLANK('By Round'!F67),"",'By Round'!F67)</f>
+        <f>IF(ISBLANK('By Round'!F52),"",'By Round'!F52)</f>
         <v/>
       </c>
       <c r="G82" s="15">
-        <f>IF(ISBLANK('By Round'!G67),"",'By Round'!G67)</f>
+        <f>IF(ISBLANK('By Round'!G52),"",'By Round'!G52)</f>
         <v/>
       </c>
       <c r="H82" s="15">
-        <f>IF(ISBLANK('By Round'!H67),"",'By Round'!H67)</f>
+        <f>IF(ISBLANK('By Round'!H52),"",'By Round'!H52)</f>
         <v/>
       </c>
       <c r="I82" s="15">
-        <f>IF(ISBLANK('By Round'!I67),"",'By Round'!I67)</f>
+        <f>IF(ISBLANK('By Round'!I52),"",'By Round'!I52)</f>
         <v/>
       </c>
       <c r="J82" s="15">
-        <f>IF(ISBLANK('By Round'!J67),"",'By Round'!J67)</f>
+        <f>IF(ISBLANK('By Round'!J52),"",'By Round'!J52)</f>
         <v/>
       </c>
       <c r="K82" s="15">
-        <f>IF(ISBLANK('By Round'!K67),"",'By Round'!K67)</f>
+        <f>IF(ISBLANK('By Round'!K52),"",'By Round'!K52)</f>
         <v/>
       </c>
       <c r="L82" s="15">
-        <f>IF(ISBLANK('By Round'!L67),"",'By Round'!L67)</f>
+        <f>IF(ISBLANK('By Round'!L52),"",'By Round'!L52)</f>
         <v/>
       </c>
       <c r="M82" s="17">
@@ -11110,47 +11110,47 @@
         <v>21</v>
       </c>
       <c r="B83" s="10">
-        <f>'By Round'!A75</f>
+        <f>'By Round'!A57</f>
         <v/>
       </c>
       <c r="C83" s="10">
-        <f>'By Round'!B75</f>
+        <f>'By Round'!B57</f>
         <v/>
       </c>
       <c r="D83" s="10">
-        <f>'By Round'!C75</f>
+        <f>'By Round'!C57</f>
         <v/>
       </c>
       <c r="E83" s="10">
-        <f>'By Round'!D75</f>
+        <f>'By Round'!D57</f>
         <v/>
       </c>
       <c r="F83" s="10">
-        <f>IF(ISBLANK('By Round'!F77),"",'By Round'!F77)</f>
+        <f>IF(ISBLANK('By Round'!F59),"",'By Round'!F59)</f>
         <v/>
       </c>
       <c r="G83">
-        <f>IF(ISBLANK('By Round'!G77),"",'By Round'!G77)</f>
+        <f>IF(ISBLANK('By Round'!G59),"",'By Round'!G59)</f>
         <v/>
       </c>
       <c r="H83">
-        <f>IF(ISBLANK('By Round'!H77),"",'By Round'!H77)</f>
+        <f>IF(ISBLANK('By Round'!H59),"",'By Round'!H59)</f>
         <v/>
       </c>
       <c r="I83">
-        <f>IF(ISBLANK('By Round'!I77),"",'By Round'!I77)</f>
+        <f>IF(ISBLANK('By Round'!I59),"",'By Round'!I59)</f>
         <v/>
       </c>
       <c r="J83">
-        <f>IF(ISBLANK('By Round'!J77),"",'By Round'!J77)</f>
+        <f>IF(ISBLANK('By Round'!J59),"",'By Round'!J59)</f>
         <v/>
       </c>
       <c r="K83">
-        <f>IF(ISBLANK('By Round'!K77),"",'By Round'!K77)</f>
+        <f>IF(ISBLANK('By Round'!K59),"",'By Round'!K59)</f>
         <v/>
       </c>
       <c r="L83">
-        <f>IF(ISBLANK('By Round'!L77),"",'By Round'!L77)</f>
+        <f>IF(ISBLANK('By Round'!L59),"",'By Round'!L59)</f>
         <v/>
       </c>
       <c r="M83" s="11">
@@ -11236,47 +11236,47 @@
     </row>
     <row r="84">
       <c r="B84" s="10">
-        <f>'By Round'!A51</f>
+        <f>'By Round'!A39</f>
         <v/>
       </c>
       <c r="C84" s="10">
-        <f>'By Round'!B57</f>
+        <f>'By Round'!B45</f>
         <v/>
       </c>
       <c r="D84" s="10">
-        <f>'By Round'!C57</f>
+        <f>'By Round'!C45</f>
         <v/>
       </c>
       <c r="E84" s="10">
-        <f>'By Round'!D57</f>
+        <f>'By Round'!D45</f>
         <v/>
       </c>
       <c r="F84" s="10">
-        <f>IF(ISBLANK('By Round'!F59),"",'By Round'!F59)</f>
+        <f>IF(ISBLANK('By Round'!F47),"",'By Round'!F47)</f>
         <v/>
       </c>
       <c r="G84">
-        <f>IF(ISBLANK('By Round'!G59),"",'By Round'!G59)</f>
+        <f>IF(ISBLANK('By Round'!G47),"",'By Round'!G47)</f>
         <v/>
       </c>
       <c r="H84">
-        <f>IF(ISBLANK('By Round'!H59),"",'By Round'!H59)</f>
+        <f>IF(ISBLANK('By Round'!H47),"",'By Round'!H47)</f>
         <v/>
       </c>
       <c r="I84">
-        <f>IF(ISBLANK('By Round'!I59),"",'By Round'!I59)</f>
+        <f>IF(ISBLANK('By Round'!I47),"",'By Round'!I47)</f>
         <v/>
       </c>
       <c r="J84">
-        <f>IF(ISBLANK('By Round'!J59),"",'By Round'!J59)</f>
+        <f>IF(ISBLANK('By Round'!J47),"",'By Round'!J47)</f>
         <v/>
       </c>
       <c r="K84">
-        <f>IF(ISBLANK('By Round'!K59),"",'By Round'!K59)</f>
+        <f>IF(ISBLANK('By Round'!K47),"",'By Round'!K47)</f>
         <v/>
       </c>
       <c r="L84">
-        <f>IF(ISBLANK('By Round'!L59),"",'By Round'!L59)</f>
+        <f>IF(ISBLANK('By Round'!L47),"",'By Round'!L47)</f>
         <v/>
       </c>
       <c r="M84" s="11">
@@ -11362,47 +11362,47 @@
     </row>
     <row r="85">
       <c r="B85" s="10">
-        <f>'By Round'!A27</f>
+        <f>'By Round'!A21</f>
         <v/>
       </c>
       <c r="C85" s="10">
-        <f>'By Round'!B36</f>
+        <f>'By Round'!B30</f>
         <v/>
       </c>
       <c r="D85" s="10">
-        <f>'By Round'!C36</f>
+        <f>'By Round'!C30</f>
         <v/>
       </c>
       <c r="E85" s="10">
-        <f>'By Round'!D36</f>
+        <f>'By Round'!D30</f>
         <v/>
       </c>
       <c r="F85" s="10">
-        <f>IF(ISBLANK('By Round'!F38),"",'By Round'!F38)</f>
+        <f>IF(ISBLANK('By Round'!F32),"",'By Round'!F32)</f>
         <v/>
       </c>
       <c r="G85">
-        <f>IF(ISBLANK('By Round'!G38),"",'By Round'!G38)</f>
+        <f>IF(ISBLANK('By Round'!G32),"",'By Round'!G32)</f>
         <v/>
       </c>
       <c r="H85">
-        <f>IF(ISBLANK('By Round'!H38),"",'By Round'!H38)</f>
+        <f>IF(ISBLANK('By Round'!H32),"",'By Round'!H32)</f>
         <v/>
       </c>
       <c r="I85">
-        <f>IF(ISBLANK('By Round'!I38),"",'By Round'!I38)</f>
+        <f>IF(ISBLANK('By Round'!I32),"",'By Round'!I32)</f>
         <v/>
       </c>
       <c r="J85">
-        <f>IF(ISBLANK('By Round'!J38),"",'By Round'!J38)</f>
+        <f>IF(ISBLANK('By Round'!J32),"",'By Round'!J32)</f>
         <v/>
       </c>
       <c r="K85">
-        <f>IF(ISBLANK('By Round'!K38),"",'By Round'!K38)</f>
+        <f>IF(ISBLANK('By Round'!K32),"",'By Round'!K32)</f>
         <v/>
       </c>
       <c r="L85">
-        <f>IF(ISBLANK('By Round'!L38),"",'By Round'!L38)</f>
+        <f>IF(ISBLANK('By Round'!L32),"",'By Round'!L32)</f>
         <v/>
       </c>
       <c r="M85" s="11">
@@ -11489,47 +11489,47 @@
     <row r="86">
       <c r="A86" s="15" t="n"/>
       <c r="B86" s="16">
-        <f>'By Round'!A63</f>
+        <f>'By Round'!A48</f>
         <v/>
       </c>
       <c r="C86" s="16">
-        <f>'By Round'!B66</f>
+        <f>'By Round'!B51</f>
         <v/>
       </c>
       <c r="D86" s="16">
-        <f>'By Round'!C66</f>
+        <f>'By Round'!C51</f>
         <v/>
       </c>
       <c r="E86" s="16">
-        <f>'By Round'!D66</f>
+        <f>'By Round'!D51</f>
         <v/>
       </c>
       <c r="F86" s="16">
-        <f>IF(ISBLANK('By Round'!F68),"",'By Round'!F68)</f>
+        <f>IF(ISBLANK('By Round'!F53),"",'By Round'!F53)</f>
         <v/>
       </c>
       <c r="G86" s="15">
-        <f>IF(ISBLANK('By Round'!G68),"",'By Round'!G68)</f>
+        <f>IF(ISBLANK('By Round'!G53),"",'By Round'!G53)</f>
         <v/>
       </c>
       <c r="H86" s="15">
-        <f>IF(ISBLANK('By Round'!H68),"",'By Round'!H68)</f>
+        <f>IF(ISBLANK('By Round'!H53),"",'By Round'!H53)</f>
         <v/>
       </c>
       <c r="I86" s="15">
-        <f>IF(ISBLANK('By Round'!I68),"",'By Round'!I68)</f>
+        <f>IF(ISBLANK('By Round'!I53),"",'By Round'!I53)</f>
         <v/>
       </c>
       <c r="J86" s="15">
-        <f>IF(ISBLANK('By Round'!J68),"",'By Round'!J68)</f>
+        <f>IF(ISBLANK('By Round'!J53),"",'By Round'!J53)</f>
         <v/>
       </c>
       <c r="K86" s="15">
-        <f>IF(ISBLANK('By Round'!K68),"",'By Round'!K68)</f>
+        <f>IF(ISBLANK('By Round'!K53),"",'By Round'!K53)</f>
         <v/>
       </c>
       <c r="L86" s="15">
-        <f>IF(ISBLANK('By Round'!L68),"",'By Round'!L68)</f>
+        <f>IF(ISBLANK('By Round'!L53),"",'By Round'!L53)</f>
         <v/>
       </c>
       <c r="M86" s="17">

--- a/howell7x3.xlsx
+++ b/howell7x3.xlsx
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 64</t>
+          <t>Name 26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 47</t>
+          <t>Name 82</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 83</t>
+          <t>Name 79</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 68</t>
+          <t>Name 20</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -636,12 +636,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 54</t>
+          <t>Name 55</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 89</t>
+          <t>Name 34</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -659,12 +659,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name 88</t>
+          <t>Name 86</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name 13</t>
+          <t>Name 70</t>
         </is>
       </c>
       <c r="D13" s="4">
@@ -682,12 +682,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name 51</t>
+          <t>Name 27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Name 71</t>
+          <t>Name 46</t>
         </is>
       </c>
       <c r="D14" s="4">
@@ -705,12 +705,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name 52</t>
+          <t>Name 55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name 39</t>
+          <t>Name 46</t>
         </is>
       </c>
       <c r="D15" s="4">
@@ -728,12 +728,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name 21</t>
+          <t>Name 83</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Name 78</t>
+          <t>Name 50</t>
         </is>
       </c>
       <c r="D16" s="4">

--- a/howell7x3.xlsx
+++ b/howell7x3.xlsx
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 26</t>
+          <t>Name 73</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 82</t>
+          <t>Name 37</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 79</t>
+          <t>Name 57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 20</t>
+          <t>Name 78</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -636,12 +636,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 55</t>
+          <t>Name 34</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 34</t>
+          <t>Name 15</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -659,12 +659,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name 86</t>
+          <t>Name 84</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name 70</t>
+          <t>Name 45</t>
         </is>
       </c>
       <c r="D13" s="4">
@@ -682,12 +682,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name 27</t>
+          <t>Name 56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Name 46</t>
+          <t>Name 11</t>
         </is>
       </c>
       <c r="D14" s="4">
@@ -705,12 +705,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name 55</t>
+          <t>Name 65</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name 46</t>
+          <t>Name 49</t>
         </is>
       </c>
       <c r="D15" s="4">
@@ -728,12 +728,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name 83</t>
+          <t>Name 49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Name 50</t>
+          <t>Name 72</t>
         </is>
       </c>
       <c r="D16" s="4">

--- a/howell7x3.xlsx
+++ b/howell7x3.xlsx
@@ -506,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Jul 29, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Jul 30, 2026.</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 73</t>
+          <t>Name 12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 37</t>
+          <t>Name 45</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 57</t>
+          <t>Name 43</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 78</t>
+          <t>Name 73</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -636,12 +636,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 34</t>
+          <t>Name 56</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 15</t>
+          <t>Name 87</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -659,12 +659,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name 84</t>
+          <t>Name 18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name 45</t>
+          <t>Name 70</t>
         </is>
       </c>
       <c r="D13" s="4">
@@ -682,12 +682,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name 56</t>
+          <t>Name 66</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Name 11</t>
+          <t>Name 41</t>
         </is>
       </c>
       <c r="D14" s="4">
@@ -705,12 +705,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name 65</t>
+          <t>Name 87</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name 49</t>
+          <t>Name 73</t>
         </is>
       </c>
       <c r="D15" s="4">
@@ -728,12 +728,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name 49</t>
+          <t>Name 30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Name 72</t>
+          <t>Name 43</t>
         </is>
       </c>
       <c r="D16" s="4">

--- a/howell7x3.xlsx
+++ b/howell7x3.xlsx
@@ -506,7 +506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>For public domain. No rights reserved. Generated on Jul 30, 2026.</t>
+          <t>For public domain. No rights reserved. Generated on Aug 05, 2026.</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Name 12</t>
+          <t>Name 14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name 45</t>
+          <t>Name 64</t>
         </is>
       </c>
       <c r="D10" s="4">
@@ -613,12 +613,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Name 43</t>
+          <t>Name 70</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name 73</t>
+          <t>Name 57</t>
         </is>
       </c>
       <c r="D11" s="4">
@@ -636,12 +636,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Name 56</t>
+          <t>Name 66</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name 87</t>
+          <t>Name 45</t>
         </is>
       </c>
       <c r="D12" s="4">
@@ -659,12 +659,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Name 18</t>
+          <t>Name 47</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name 70</t>
+          <t>Name 81</t>
         </is>
       </c>
       <c r="D13" s="4">
@@ -682,12 +682,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Name 66</t>
+          <t>Name 22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Name 41</t>
+          <t>Name 27</t>
         </is>
       </c>
       <c r="D14" s="4">
@@ -705,12 +705,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Name 87</t>
+          <t>Name 11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Name 73</t>
+          <t>Name 45</t>
         </is>
       </c>
       <c r="D15" s="4">
@@ -728,12 +728,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Name 30</t>
+          <t>Name 84</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Name 43</t>
+          <t>Name 78</t>
         </is>
       </c>
       <c r="D16" s="4">
@@ -13687,15 +13687,15 @@
         <v/>
       </c>
       <c r="N4">
-        <f>K3-100</f>
+        <f>N3-100</f>
         <v/>
       </c>
       <c r="O4">
-        <f>L3-300</f>
+        <f>O3-300</f>
         <v/>
       </c>
       <c r="P4">
-        <f>L4*2</f>
+        <f>O4*2</f>
         <v/>
       </c>
     </row>
@@ -13737,15 +13737,15 @@
         <v/>
       </c>
       <c r="N5">
-        <f>K4-100</f>
+        <f>N4-100</f>
         <v/>
       </c>
       <c r="O5">
-        <f>L4-300</f>
+        <f>O4-300</f>
         <v/>
       </c>
       <c r="P5">
-        <f>L5*2</f>
+        <f>O5*2</f>
         <v/>
       </c>
     </row>
@@ -13787,15 +13787,15 @@
         <v/>
       </c>
       <c r="N6">
-        <f>K5-100</f>
+        <f>N5-100</f>
         <v/>
       </c>
       <c r="O6">
-        <f>L5-300</f>
+        <f>O5-300</f>
         <v/>
       </c>
       <c r="P6">
-        <f>L6*2</f>
+        <f>O6*2</f>
         <v/>
       </c>
     </row>
@@ -13837,15 +13837,15 @@
         <v/>
       </c>
       <c r="N7">
-        <f>K6-100</f>
+        <f>N6-100</f>
         <v/>
       </c>
       <c r="O7">
-        <f>L6-300</f>
+        <f>O6-300</f>
         <v/>
       </c>
       <c r="P7">
-        <f>L7*2</f>
+        <f>O7*2</f>
         <v/>
       </c>
     </row>
@@ -13887,15 +13887,15 @@
         <v/>
       </c>
       <c r="N8">
-        <f>K7-100</f>
+        <f>N7-100</f>
         <v/>
       </c>
       <c r="O8">
-        <f>L7-300</f>
+        <f>O7-300</f>
         <v/>
       </c>
       <c r="P8">
-        <f>L8*2</f>
+        <f>O8*2</f>
         <v/>
       </c>
     </row>
@@ -13937,15 +13937,15 @@
         <v/>
       </c>
       <c r="N9">
-        <f>K8-100</f>
+        <f>N8-100</f>
         <v/>
       </c>
       <c r="O9">
-        <f>L8-300</f>
+        <f>O8-300</f>
         <v/>
       </c>
       <c r="P9">
-        <f>L9*2</f>
+        <f>O9*2</f>
         <v/>
       </c>
     </row>
@@ -13992,15 +13992,15 @@
         <v/>
       </c>
       <c r="N10">
-        <f>K9-100</f>
+        <f>N9-100</f>
         <v/>
       </c>
       <c r="O10">
-        <f>L9-300</f>
+        <f>O9-300</f>
         <v/>
       </c>
       <c r="P10">
-        <f>L10*2</f>
+        <f>O10*2</f>
         <v/>
       </c>
     </row>
@@ -14042,15 +14042,15 @@
         <v/>
       </c>
       <c r="N11">
-        <f>K10-100</f>
+        <f>N10-100</f>
         <v/>
       </c>
       <c r="O11">
-        <f>L10-300</f>
+        <f>O10-300</f>
         <v/>
       </c>
       <c r="P11">
-        <f>L11*2</f>
+        <f>O11*2</f>
         <v/>
       </c>
     </row>
@@ -14092,15 +14092,15 @@
         <v/>
       </c>
       <c r="N12">
-        <f>K11-100</f>
+        <f>N11-100</f>
         <v/>
       </c>
       <c r="O12">
-        <f>L11-300</f>
+        <f>O11-300</f>
         <v/>
       </c>
       <c r="P12">
-        <f>L12*2</f>
+        <f>O12*2</f>
         <v/>
       </c>
     </row>
@@ -14142,15 +14142,15 @@
         <v/>
       </c>
       <c r="N13">
-        <f>K12-100</f>
+        <f>N12-100</f>
         <v/>
       </c>
       <c r="O13">
-        <f>L12-300</f>
+        <f>O12-300</f>
         <v/>
       </c>
       <c r="P13">
-        <f>L13*2</f>
+        <f>O13*2</f>
         <v/>
       </c>
     </row>
@@ -14192,15 +14192,15 @@
         <v/>
       </c>
       <c r="N14">
-        <f>K13-100</f>
+        <f>N13-100</f>
         <v/>
       </c>
       <c r="O14">
-        <f>L13-300</f>
+        <f>O13-300</f>
         <v/>
       </c>
       <c r="P14">
-        <f>L14*2</f>
+        <f>O14*2</f>
         <v/>
       </c>
     </row>
@@ -14242,15 +14242,15 @@
         <v/>
       </c>
       <c r="N15">
-        <f>K14-100</f>
+        <f>N14-100</f>
         <v/>
       </c>
       <c r="O15">
-        <f>L14-300</f>
+        <f>O14-300</f>
         <v/>
       </c>
       <c r="P15">
-        <f>L15*2</f>
+        <f>O15*2</f>
         <v/>
       </c>
     </row>
